--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D4CE66-801A-4FA1-A4DF-4E0F5B2548CB}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F04212-DF8F-4BA3-B3F7-A8E1CC19154C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Pivots" sheetId="2" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="4" r:id="rId2"/>
     <sheet name="Ecommerce_Data" sheetId="1" r:id="rId3"/>
   </sheets>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1162,7 +1162,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1265,13 +1265,12 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1287,6 +1286,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1299,7 +1299,7 @@
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1328,7 +1328,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[ecommerce_dataset.xlsx]Sheet1!PivotTable1</c:name>
+    <c:name>[ecommerce_dataset.xlsx]Pivots!by cetegory</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -1569,7 +1569,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$3</c:f>
+              <c:f>Pivots!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1590,7 +1590,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$4:$A$7</c:f>
+              <c:f>Pivots!$B$4:$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1607,7 +1607,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$4:$B$7</c:f>
+              <c:f>Pivots!$C$4:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1860,7 +1860,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[ecommerce_dataset.xlsx]Sheet1!PivotTable4</c:name>
+    <c:name>[ecommerce_dataset.xlsx]Pivots!monthly sales</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -2106,7 +2106,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$13</c:f>
+              <c:f>Pivots!$C$36</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2129,7 +2129,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$14:$G$26</c:f>
+              <c:f>Pivots!$B$37:$B$49</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2173,7 +2173,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$14:$H$26</c:f>
+              <c:f>Pivots!$C$37:$C$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2454,7 +2454,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[ecommerce_dataset.xlsx]Sheet1!PivotTable3</c:name>
+    <c:name>[ecommerce_dataset.xlsx]Pivots!by_city</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -2695,7 +2695,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$13</c:f>
+              <c:f>Pivots!$C$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2716,7 +2716,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$14:$A$21</c:f>
+              <c:f>Pivots!$B$12:$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -2745,7 +2745,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$14:$B$21</c:f>
+              <c:f>Pivots!$C$12:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3011,7 +3011,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[ecommerce_dataset.xlsx]Sheet1!PivotTable5</c:name>
+    <c:name>[ecommerce_dataset.xlsx]Pivots!by product</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -3338,6 +3338,76 @@
           <a:effectLst/>
         </c:spPr>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3348,7 +3418,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$13</c:f>
+              <c:f>Pivots!$C$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3431,6 +3501,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-75F4-4F4F-8A86-0FF1A08E23E3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -3446,6 +3521,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-75F4-4F4F-8A86-0FF1A08E23E3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -3461,6 +3541,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-75F4-4F4F-8A86-0FF1A08E23E3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -3478,6 +3563,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-75F4-4F4F-8A86-0FF1A08E23E3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -3495,6 +3585,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-75F4-4F4F-8A86-0FF1A08E23E3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3554,7 +3649,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$D$14:$D$22</c:f>
+              <c:f>Pivots!$B$24:$B$32</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3586,7 +3681,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$22</c:f>
+              <c:f>Pivots!$C$24:$C$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -6103,8 +6198,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>161926</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="City">
@@ -6127,7 +6222,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6181,8 +6276,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Category">
@@ -6205,7 +6300,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6259,8 +6354,8 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Month">
@@ -6283,7 +6378,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6336,7 +6431,7 @@
     <cacheField name="Order ID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1600"/>
     </cacheField>
-    <cacheField name="Order Date" numFmtId="170">
+    <cacheField name="Order Date" numFmtId="164">
       <sharedItems/>
     </cacheField>
     <cacheField name="Customer Name" numFmtId="0">
@@ -14228,136 +14323,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="PivotTable6" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J14:K27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="8"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="PivotTable5" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="D13:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B23:C32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14455,7 +14422,7 @@
   <dataFields count="1">
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="10">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -14510,6 +14477,66 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="4" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -14523,9 +14550,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="G13:H26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14655,9 +14682,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A13:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14772,9 +14799,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14877,14 +14904,142 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="top cunsumer" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B53:C66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="8"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{D33028C7-68A4-43A0-B516-720506AAE5EF}" sourceName="City">
   <pivotTables>
-    <pivotTable tabId="2" name="PivotTable3"/>
-    <pivotTable tabId="2" name="PivotTable1"/>
-    <pivotTable tabId="2" name="PivotTable4"/>
-    <pivotTable tabId="2" name="PivotTable5"/>
-    <pivotTable tabId="2" name="PivotTable6"/>
+    <pivotTable tabId="2" name="by_city"/>
+    <pivotTable tabId="2" name="by cetegory"/>
+    <pivotTable tabId="2" name="monthly sales"/>
+    <pivotTable tabId="2" name="by product"/>
+    <pivotTable tabId="2" name="top cunsumer"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="601249990">
@@ -14905,11 +15060,11 @@
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{A402FCD2-D5D0-44C5-A069-E9333FF13B22}" sourceName="Category">
   <pivotTables>
-    <pivotTable tabId="2" name="PivotTable3"/>
-    <pivotTable tabId="2" name="PivotTable1"/>
-    <pivotTable tabId="2" name="PivotTable4"/>
-    <pivotTable tabId="2" name="PivotTable5"/>
-    <pivotTable tabId="2" name="PivotTable6"/>
+    <pivotTable tabId="2" name="by_city"/>
+    <pivotTable tabId="2" name="by cetegory"/>
+    <pivotTable tabId="2" name="monthly sales"/>
+    <pivotTable tabId="2" name="by product"/>
+    <pivotTable tabId="2" name="top cunsumer"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="601249990">
@@ -14926,11 +15081,11 @@
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{EF836BAC-2648-451C-868E-04E11FD8359F}" sourceName="Month">
   <pivotTables>
-    <pivotTable tabId="2" name="PivotTable3"/>
-    <pivotTable tabId="2" name="PivotTable1"/>
-    <pivotTable tabId="2" name="PivotTable4"/>
-    <pivotTable tabId="2" name="PivotTable5"/>
-    <pivotTable tabId="2" name="PivotTable6"/>
+    <pivotTable tabId="2" name="by_city"/>
+    <pivotTable tabId="2" name="by cetegory"/>
+    <pivotTable tabId="2" name="monthly sales"/>
+    <pivotTable tabId="2" name="by product"/>
+    <pivotTable tabId="2" name="top cunsumer"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="601249990">
@@ -15269,368 +15424,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF3CD5B-B6B3-48EA-8FE8-F51E21FA5F4E}">
-  <dimension ref="A3:K27"/>
+  <dimension ref="B3:C66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="5">
+      <c r="C4" s="10">
         <v>1385000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5">
+      <c r="C5" s="10">
         <v>16567500</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="C6" s="10">
         <v>1205600</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="5">
+      <c r="C7" s="10">
         <v>19158100</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C11" t="s">
         <v>353</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2737200</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10">
+        <v>2996300</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1914000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="10">
+        <v>3072800</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2920500</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2604000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2913300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C19" s="10">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E13" t="s">
+      <c r="C23" t="s">
         <v>353</v>
       </c>
-      <c r="G13" s="3" t="s">
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="10">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="10">
+        <v>587500</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="10">
+        <v>414000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="10">
+        <v>11400000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="10">
+        <v>4580000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="10">
+        <v>606000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="10">
+        <v>185600</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="10">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" s="10">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="H13" t="s">
+      <c r="C36" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5">
-        <v>2737200</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="5">
-        <v>315000</v>
-      </c>
-      <c r="G14" s="4" t="s">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="H14" s="5">
+      <c r="C37" s="10">
         <v>2075900</v>
       </c>
-      <c r="J14" s="3" t="s">
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" s="10">
+        <v>1004500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="10">
+        <v>1088700</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C40" s="10">
+        <v>1215100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C41" s="10">
+        <v>1553100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2927200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C43" s="10">
+        <v>1340000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C44" s="10">
+        <v>1671200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C45" s="10">
+        <v>1662900</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C46" s="10">
+        <v>1699400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47" s="10">
+        <v>1319900</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48" s="10">
+        <v>1600200</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C49" s="10">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="K14" t="s">
+      <c r="C53" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="5">
-        <v>2996300</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="5">
-        <v>587500</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="H15" s="5">
-        <v>1004500</v>
-      </c>
-      <c r="J15" s="4" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="5">
+      <c r="C54" s="10">
         <v>749900</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="5">
-        <v>1914000</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="5">
-        <v>414000</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H16" s="5">
-        <v>1088700</v>
-      </c>
-      <c r="J16" s="4" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="5">
+      <c r="C55" s="10">
         <v>1526900</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="5">
-        <v>3072800</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5">
-        <v>11400000</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H17" s="5">
-        <v>1215100</v>
-      </c>
-      <c r="J17" s="4" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="5">
+      <c r="C56" s="10">
         <v>1139000</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="5">
-        <v>2920500</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="5">
-        <v>4580000</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="H18" s="5">
-        <v>1553100</v>
-      </c>
-      <c r="J18" s="4" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="5">
+      <c r="C57" s="10">
         <v>2066300</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="5">
-        <v>2604000</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="5">
-        <v>606000</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="H19" s="5">
-        <v>2927200</v>
-      </c>
-      <c r="J19" s="4" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K19" s="5">
+      <c r="C58" s="10">
         <v>1121800</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="5">
-        <v>2913300</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="5">
-        <v>185600</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="H20" s="5">
-        <v>1340000</v>
-      </c>
-      <c r="J20" s="4" t="s">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K20" s="5">
+      <c r="C59" s="10">
         <v>2391600</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" s="10">
+        <v>1752800</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="10">
+        <v>934900</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="10">
+        <v>1588100</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="10">
+        <v>3068200</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="10">
+        <v>1144000</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="10">
+        <v>1674600</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B21" s="5">
-        <v>19158100</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1070000</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1671200</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" s="5">
-        <v>1752800</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="E22" s="5">
-        <v>19158100</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="H22" s="5">
-        <v>1662900</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="5">
-        <v>934900</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G23" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="H23" s="5">
-        <v>1699400</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" s="5">
-        <v>1588100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G24" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="H24" s="5">
-        <v>1319900</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K24" s="5">
-        <v>3068200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G25" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="H25" s="5">
-        <v>1600200</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="5">
-        <v>1144000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G26" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="H26" s="5">
-        <v>19158100</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="5">
-        <v>1674600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J27" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="K27" s="5">
+      <c r="C66" s="10">
         <v>19158100</v>
       </c>
     </row>
@@ -15645,42 +15864,42 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <f>SUM(Ecommerce_Data[Total Sales])</f>
         <v>19158100</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="F3" s="7">
+      <c r="C3" s="7"/>
+      <c r="F3" s="6">
         <f>COUNTA(Ecommerce_Data[Order ID])</f>
         <v>600</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="J3" s="7">
+      <c r="G3" s="7"/>
+      <c r="J3" s="6">
         <f>SUM(Ecommerce_Data[Quantity])</f>
         <v>1757</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15690,11 +15909,12 @@
     <mergeCell ref="J3:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F04212-DF8F-4BA3-B3F7-A8E1CC19154C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FFC3FEC-657D-4A95-BD70-5E2DC6D8BB33}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivots" sheetId="2" r:id="rId1"/>
@@ -6265,19 +6265,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Category">
@@ -6300,7 +6300,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6310,7 +6310,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7467600" y="76200"/>
+              <a:off x="8382000" y="85725"/>
               <a:ext cx="1828800" cy="1190625"/>
             </a:xfrm>
             <a:prstGeom prst="rect">

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FFC3FEC-657D-4A95-BD70-5E2DC6D8BB33}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481C162B-5B4E-4192-8177-820794BAAB22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   <definedNames>
     <definedName name="Slicer_Category">#N/A</definedName>
     <definedName name="Slicer_City">#N/A</definedName>
-    <definedName name="Slicer_Month">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -31,7 +30,6 @@
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId5"/>
         <x14:slicerCache r:id="rId6"/>
-        <x14:slicerCache r:id="rId7"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -51,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3070" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="367">
   <si>
     <t>Order ID</t>
   </si>
@@ -1151,9 +1149,6 @@
     <t>Dec</t>
   </si>
   <si>
-    <t>E-Commerce Sales Dashboard</t>
-  </si>
-  <si>
     <t>Profit</t>
   </si>
 </sst>
@@ -1161,10 +1156,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1178,36 +1174,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1215,55 +1191,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1271,27 +1203,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="29">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1303,6 +1298,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFBE5E9"/>
+      <color rgb="FFFADADF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1318,13 +1319,13 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="104"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="4"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -1339,9 +1340,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
+                  <a:schemeClr val="dk1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
@@ -1352,8 +1353,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Sales By Cetegory</a:t>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> CETEGORICAL SHARE</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1371,9 +1372,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="dk1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
@@ -1391,17 +1392,54 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="25000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1419,12 +1457,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1438,119 +1473,7 @@
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
@@ -1560,10 +1483,8 @@
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1578,16 +1499,119 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:tint val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="25000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
               <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Pivots!$B$4:$B$7</c:f>
@@ -1609,7 +1633,7 @@
             <c:numRef>
               <c:f>Pivots!$C$4:$C$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1385000</c:v>
@@ -1634,120 +1658,13 @@
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="327972095"/>
-        <c:axId val="327974015"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="327972095"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="327974015"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="327974015"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="327972095"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="70"/>
+      </c:doughnutChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1757,10 +1674,14 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="78000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1773,7 +1694,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="dk1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
@@ -1799,19 +1720,32 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -1850,13 +1784,13 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="104"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="4"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -1871,12 +1805,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1903,12 +1834,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1923,20 +1851,64 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
+          <a:ln w="34925" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+              <a:schemeClr val="accent2"/>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1954,127 +1926,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -2116,16 +1970,33 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent2"/>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="22225">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:strRef>
@@ -2175,7 +2046,7 @@
             <c:numRef>
               <c:f>Pivots!$C$37:$C$49</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2075900</c:v>
@@ -2231,6 +2102,28 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="331457039"/>
         <c:axId val="331458479"/>
@@ -2248,12 +2141,9 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2264,12 +2154,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2293,21 +2180,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2325,10 +2198,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2350,37 +2220,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2393,19 +2232,33 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:pattFill prst="dotDmnd">
+      <a:fgClr>
+        <a:srgbClr val="FF0000"/>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="accent6">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:bgClr>
+    </a:pattFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+    <a:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="freezing" dir="t"/>
+    </a:scene3d>
+    <a:sp3d/>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -2428,7 +2281,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -2444,13 +2296,13 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="104"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="4"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -2465,11 +2317,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -2497,11 +2349,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -2517,17 +2369,69 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent2"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent2"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2560,118 +2464,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2705,13 +2498,25 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:pattFill prst="narHorz">
+              <a:fgClr>
+                <a:schemeClr val="accent2"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:innerShdw blurRad="114300">
+                <a:schemeClr val="accent2"/>
+              </a:innerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
@@ -2747,7 +2552,7 @@
             <c:numRef>
               <c:f>Pivots!$C$12:$C$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2737200</c:v>
@@ -2780,6 +2585,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2787,8 +2593,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="164"/>
+        <c:overlap val="-22"/>
         <c:axId val="335778015"/>
         <c:axId val="335798175"/>
       </c:barChart>
@@ -2805,11 +2611,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -2850,21 +2656,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2901,43 +2693,12 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln cap="rnd">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2950,19 +2711,25 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:pattFill prst="pct5">
+      <a:fgClr>
+        <a:srgbClr val="FBE5E9"/>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="bg1"/>
+      </a:bgClr>
+    </a:pattFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -2985,7 +2752,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -3001,7 +2767,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -3022,11 +2788,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3036,13 +2802,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>Cetegorical</a:t>
+              <a:t>PRODUCT Share</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-IN" baseline="0"/>
-              <a:t> Share</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-IN"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3059,11 +2820,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -3079,19 +2840,73 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3126,170 +2941,10 @@
           </c:txPr>
           <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="bestFit"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="bestFit"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
@@ -3299,119 +2954,226 @@
       <c:pivotFmt>
         <c:idx val="6"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent2"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent2"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="7"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent4"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent4"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent5"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent5"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="9"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="10"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent3"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent3"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="11"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent6"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent6"/>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="12"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="13"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
           <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:innerShdw>
+          </a:effectLst>
         </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:pieChart>
+      <c:ofPieChart>
+        <c:ofPieType val="pie"/>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -3431,15 +3193,27 @@
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent1"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent1"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3451,15 +3225,27 @@
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent2"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent2"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3471,15 +3257,27 @@
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent3"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3491,15 +3289,27 @@
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent4"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent4"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3511,15 +3321,27 @@
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent5"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent5"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3531,15 +3353,27 @@
             <c:idx val="5"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent6"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent6"/>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3551,17 +3385,32 @@
             <c:idx val="6"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3573,23 +3422,70 @@
             <c:idx val="7"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:innerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000000F-75F4-4F4F-8A86-0FF1A08E23E3}"/>
               </c:ext>
             </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3623,22 +3519,21 @@
             </c:txPr>
             <c:dLblPos val="bestFit"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
+            <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:ln w="9525">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="35000"/>
                       <a:lumOff val="65000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:round/>
                 </a:ln>
                 <a:effectLst/>
               </c:spPr>
@@ -3683,7 +3578,7 @@
             <c:numRef>
               <c:f>Pivots!$C$24:$C$32</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>315000</c:v>
@@ -3719,7 +3614,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -3728,8 +3622,23 @@
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:gapWidth val="100"/>
+        <c:secondPieSize val="75"/>
+        <c:serLines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:serLines>
+      </c:ofPieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -3781,9 +3690,14 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:pattFill prst="pct10">
+      <a:fgClr>
+        <a:srgbClr val="FBE5E9"/>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="bg1"/>
+      </a:bgClr>
+    </a:pattFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -3793,7 +3707,13 @@
       </a:solidFill>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
@@ -3829,122 +3749,20 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -3989,33 +3807,52 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
     <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -4024,41 +3861,15 @@
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -4072,9 +3883,11 @@
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
@@ -4090,32 +3903,61 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="28575" cap="rnd">
@@ -4127,33 +3969,34 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -4169,7 +4012,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
@@ -4178,525 +4021,7 @@
       <a:noFill/>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
           <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -4716,17 +4041,18 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -4735,12 +4061,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -4754,12 +4080,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -4773,7 +4099,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:noFill/>
@@ -4787,12 +4113,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -4806,12 +4132,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
@@ -4825,14 +4151,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -4844,12 +4170,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -4863,11 +4189,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
   <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
@@ -4875,7 +4208,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -4883,7 +4216,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -4891,7 +4224,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
@@ -4903,12 +4236,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
@@ -4922,12 +4255,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -4936,14 +4269,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -4952,7 +4285,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
@@ -4970,13 +4303,14 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4985,7 +4319,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="dk1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
@@ -4997,20 +4331,543 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5021,7 +4878,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -5034,11 +4891,11 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5051,510 +4908,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -5614,36 +4968,60 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -5653,7 +5031,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="28575" cap="rnd">
@@ -5665,25 +5043,21 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -5691,7 +5065,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -5713,15 +5087,13 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5731,7 +5103,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -5740,14 +5112,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -5756,10 +5127,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -5775,14 +5146,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5794,31 +5165,24 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMajor>
@@ -5827,17 +5191,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -5846,14 +5209,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5865,17 +5228,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -5896,7 +5258,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -5904,7 +5266,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -5924,10 +5286,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -5944,11 +5306,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -5957,14 +5319,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -5985,20 +5346,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6019,14 +5379,542 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="252">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -6036,15 +5924,1124 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A553A88E-61BA-8040-7621-875B4D494A78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19051" y="47624"/>
+          <a:ext cx="12215131" cy="6512963"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="csX0" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY0" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX1" fmla="*/ 459522 w 12215131"/>
+            <a:gd name="csY1" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX2" fmla="*/ 796892 w 12215131"/>
+            <a:gd name="csY2" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX3" fmla="*/ 1256413 w 12215131"/>
+            <a:gd name="csY3" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX4" fmla="*/ 1715935 w 12215131"/>
+            <a:gd name="csY4" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX5" fmla="*/ 2297608 w 12215131"/>
+            <a:gd name="csY5" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX6" fmla="*/ 3123583 w 12215131"/>
+            <a:gd name="csY6" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX7" fmla="*/ 3338802 w 12215131"/>
+            <a:gd name="csY7" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX8" fmla="*/ 4164778 w 12215131"/>
+            <a:gd name="csY8" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX9" fmla="*/ 4502148 w 12215131"/>
+            <a:gd name="csY9" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX10" fmla="*/ 5205972 w 12215131"/>
+            <a:gd name="csY10" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX11" fmla="*/ 5787645 w 12215131"/>
+            <a:gd name="csY11" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX12" fmla="*/ 6613621 w 12215131"/>
+            <a:gd name="csY12" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX13" fmla="*/ 7317445 w 12215131"/>
+            <a:gd name="csY13" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX14" fmla="*/ 7532664 w 12215131"/>
+            <a:gd name="csY14" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX15" fmla="*/ 7870034 w 12215131"/>
+            <a:gd name="csY15" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX16" fmla="*/ 8451707 w 12215131"/>
+            <a:gd name="csY16" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX17" fmla="*/ 8789078 w 12215131"/>
+            <a:gd name="csY17" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX18" fmla="*/ 9492902 w 12215131"/>
+            <a:gd name="csY18" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX19" fmla="*/ 10196726 w 12215131"/>
+            <a:gd name="csY19" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX20" fmla="*/ 10411945 w 12215131"/>
+            <a:gd name="csY20" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX21" fmla="*/ 11115769 w 12215131"/>
+            <a:gd name="csY21" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX22" fmla="*/ 11453139 w 12215131"/>
+            <a:gd name="csY22" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX23" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY23" fmla="*/ 0 h 6512963"/>
+            <a:gd name="csX24" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY24" fmla="*/ 592088 h 6512963"/>
+            <a:gd name="csX25" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY25" fmla="*/ 1053916 h 6512963"/>
+            <a:gd name="csX26" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY26" fmla="*/ 1580874 h 6512963"/>
+            <a:gd name="csX27" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY27" fmla="*/ 2238091 h 6512963"/>
+            <a:gd name="csX28" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY28" fmla="*/ 2634790 h 6512963"/>
+            <a:gd name="csX29" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY29" fmla="*/ 3161747 h 6512963"/>
+            <a:gd name="csX30" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY30" fmla="*/ 3688705 h 6512963"/>
+            <a:gd name="csX31" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY31" fmla="*/ 4150534 h 6512963"/>
+            <a:gd name="csX32" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY32" fmla="*/ 4872880 h 6512963"/>
+            <a:gd name="csX33" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY33" fmla="*/ 5595227 h 6512963"/>
+            <a:gd name="csX34" fmla="*/ 12215131 w 12215131"/>
+            <a:gd name="csY34" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX35" fmla="*/ 11755609 w 12215131"/>
+            <a:gd name="csY35" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX36" fmla="*/ 11173937 w 12215131"/>
+            <a:gd name="csY36" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX37" fmla="*/ 10836566 w 12215131"/>
+            <a:gd name="csY37" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX38" fmla="*/ 10132742 w 12215131"/>
+            <a:gd name="csY38" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX39" fmla="*/ 9428918 w 12215131"/>
+            <a:gd name="csY39" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX40" fmla="*/ 8602942 w 12215131"/>
+            <a:gd name="csY40" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX41" fmla="*/ 8265572 w 12215131"/>
+            <a:gd name="csY41" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX42" fmla="*/ 7561748 w 12215131"/>
+            <a:gd name="csY42" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX43" fmla="*/ 6857924 w 12215131"/>
+            <a:gd name="csY43" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX44" fmla="*/ 6276251 w 12215131"/>
+            <a:gd name="csY44" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX45" fmla="*/ 5450275 w 12215131"/>
+            <a:gd name="csY45" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX46" fmla="*/ 4624300 w 12215131"/>
+            <a:gd name="csY46" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX47" fmla="*/ 3920475 w 12215131"/>
+            <a:gd name="csY47" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX48" fmla="*/ 3460954 w 12215131"/>
+            <a:gd name="csY48" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX49" fmla="*/ 3001432 w 12215131"/>
+            <a:gd name="csY49" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX50" fmla="*/ 2175457 w 12215131"/>
+            <a:gd name="csY50" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX51" fmla="*/ 1349481 w 12215131"/>
+            <a:gd name="csY51" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX52" fmla="*/ 767808 w 12215131"/>
+            <a:gd name="csY52" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX53" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY53" fmla="*/ 6512963 h 6512963"/>
+            <a:gd name="csX54" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY54" fmla="*/ 5855746 h 6512963"/>
+            <a:gd name="csX55" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY55" fmla="*/ 5328788 h 6512963"/>
+            <a:gd name="csX56" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY56" fmla="*/ 4606441 h 6512963"/>
+            <a:gd name="csX57" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY57" fmla="*/ 4079483 h 6512963"/>
+            <a:gd name="csX58" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY58" fmla="*/ 3682785 h 6512963"/>
+            <a:gd name="csX59" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY59" fmla="*/ 3220956 h 6512963"/>
+            <a:gd name="csX60" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY60" fmla="*/ 2628869 h 6512963"/>
+            <a:gd name="csX61" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY61" fmla="*/ 1971652 h 6512963"/>
+            <a:gd name="csX62" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY62" fmla="*/ 1314434 h 6512963"/>
+            <a:gd name="csX63" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY63" fmla="*/ 722347 h 6512963"/>
+            <a:gd name="csX64" fmla="*/ 0 w 12215131"/>
+            <a:gd name="csY64" fmla="*/ 0 h 6512963"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="csX0" y="csY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX1" y="csY1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX2" y="csY2"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX3" y="csY3"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX4" y="csY4"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX5" y="csY5"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX6" y="csY6"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX7" y="csY7"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX8" y="csY8"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX9" y="csY9"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX10" y="csY10"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX11" y="csY11"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX12" y="csY12"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX13" y="csY13"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX14" y="csY14"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX15" y="csY15"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX16" y="csY16"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX17" y="csY17"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX18" y="csY18"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX19" y="csY19"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX20" y="csY20"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX21" y="csY21"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX22" y="csY22"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX23" y="csY23"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX24" y="csY24"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX25" y="csY25"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX26" y="csY26"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX27" y="csY27"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX28" y="csY28"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX29" y="csY29"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX30" y="csY30"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX31" y="csY31"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX32" y="csY32"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX33" y="csY33"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX34" y="csY34"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX35" y="csY35"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX36" y="csY36"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX37" y="csY37"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX38" y="csY38"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX39" y="csY39"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX40" y="csY40"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX41" y="csY41"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX42" y="csY42"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX43" y="csY43"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX44" y="csY44"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX45" y="csY45"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX46" y="csY46"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX47" y="csY47"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX48" y="csY48"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX49" y="csY49"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX50" y="csY50"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX51" y="csY51"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX52" y="csY52"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX53" y="csY53"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX54" y="csY54"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX55" y="csY55"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX56" y="csY56"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX57" y="csY57"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX58" y="csY58"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX59" y="csY59"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX60" y="csY60"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX61" y="csY61"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX62" y="csY62"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX63" y="csY63"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX64" y="csY64"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="12215131" h="6512963" fill="none" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="0" y="0"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="160982" y="-52316"/>
+                <a:pt x="360012" y="11304"/>
+                <a:pt x="459522" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="559032" y="-11304"/>
+                <a:pt x="668369" y="33162"/>
+                <a:pt x="796892" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="925415" y="-33162"/>
+                <a:pt x="1117271" y="49342"/>
+                <a:pt x="1256413" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1395555" y="-49342"/>
+                <a:pt x="1490986" y="42850"/>
+                <a:pt x="1715935" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1940884" y="-42850"/>
+                <a:pt x="2080976" y="23529"/>
+                <a:pt x="2297608" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2514240" y="-23529"/>
+                <a:pt x="2759651" y="61282"/>
+                <a:pt x="3123583" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3487516" y="-61282"/>
+                <a:pt x="3248711" y="15334"/>
+                <a:pt x="3338802" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3428893" y="-15334"/>
+                <a:pt x="3795121" y="59940"/>
+                <a:pt x="4164778" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4534435" y="-59940"/>
+                <a:pt x="4368924" y="12520"/>
+                <a:pt x="4502148" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4635372" y="-12520"/>
+                <a:pt x="4952893" y="60275"/>
+                <a:pt x="5205972" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5459051" y="-60275"/>
+                <a:pt x="5632739" y="18533"/>
+                <a:pt x="5787645" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5942551" y="-18533"/>
+                <a:pt x="6387955" y="1242"/>
+                <a:pt x="6613621" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6839287" y="-1242"/>
+                <a:pt x="7162640" y="61687"/>
+                <a:pt x="7317445" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7472250" y="-61687"/>
+                <a:pt x="7488438" y="18818"/>
+                <a:pt x="7532664" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7576890" y="-18818"/>
+                <a:pt x="7723612" y="14886"/>
+                <a:pt x="7870034" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8016456" y="-14886"/>
+                <a:pt x="8318160" y="44187"/>
+                <a:pt x="8451707" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8585254" y="-44187"/>
+                <a:pt x="8655169" y="38077"/>
+                <a:pt x="8789078" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8922987" y="-38077"/>
+                <a:pt x="9292751" y="41177"/>
+                <a:pt x="9492902" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9693053" y="-41177"/>
+                <a:pt x="9855510" y="84096"/>
+                <a:pt x="10196726" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10537942" y="-84096"/>
+                <a:pt x="10349780" y="10480"/>
+                <a:pt x="10411945" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10474110" y="-10480"/>
+                <a:pt x="10815501" y="39316"/>
+                <a:pt x="11115769" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11416037" y="-39316"/>
+                <a:pt x="11363723" y="24150"/>
+                <a:pt x="11453139" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11542555" y="-24150"/>
+                <a:pt x="12055011" y="80263"/>
+                <a:pt x="12215131" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12238227" y="163119"/>
+                <a:pt x="12171369" y="461863"/>
+                <a:pt x="12215131" y="592088"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12258893" y="722313"/>
+                <a:pt x="12172524" y="857737"/>
+                <a:pt x="12215131" y="1053916"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12257738" y="1250095"/>
+                <a:pt x="12178761" y="1432438"/>
+                <a:pt x="12215131" y="1580874"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12251501" y="1729310"/>
+                <a:pt x="12166905" y="2030253"/>
+                <a:pt x="12215131" y="2238091"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12263357" y="2445929"/>
+                <a:pt x="12200721" y="2538680"/>
+                <a:pt x="12215131" y="2634790"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12229541" y="2730900"/>
+                <a:pt x="12203806" y="2916131"/>
+                <a:pt x="12215131" y="3161747"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12226456" y="3407363"/>
+                <a:pt x="12168836" y="3497237"/>
+                <a:pt x="12215131" y="3688705"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12261426" y="3880173"/>
+                <a:pt x="12206997" y="4008476"/>
+                <a:pt x="12215131" y="4150534"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12223265" y="4292592"/>
+                <a:pt x="12204348" y="4588728"/>
+                <a:pt x="12215131" y="4872880"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12225914" y="5157032"/>
+                <a:pt x="12191415" y="5449768"/>
+                <a:pt x="12215131" y="5595227"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12238847" y="5740686"/>
+                <a:pt x="12164226" y="6293349"/>
+                <a:pt x="12215131" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12004265" y="6513113"/>
+                <a:pt x="11870921" y="6464037"/>
+                <a:pt x="11755609" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11640297" y="6561889"/>
+                <a:pt x="11448664" y="6450726"/>
+                <a:pt x="11173937" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10899210" y="6575200"/>
+                <a:pt x="10958171" y="6506625"/>
+                <a:pt x="10836566" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10714961" y="6519301"/>
+                <a:pt x="10329423" y="6487662"/>
+                <a:pt x="10132742" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9936061" y="6538264"/>
+                <a:pt x="9620997" y="6500905"/>
+                <a:pt x="9428918" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9236839" y="6525021"/>
+                <a:pt x="9010500" y="6486906"/>
+                <a:pt x="8602942" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8195384" y="6539020"/>
+                <a:pt x="8346636" y="6498864"/>
+                <a:pt x="8265572" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8184508" y="6527062"/>
+                <a:pt x="7828575" y="6481481"/>
+                <a:pt x="7561748" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7294921" y="6544445"/>
+                <a:pt x="7028495" y="6494046"/>
+                <a:pt x="6857924" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6687353" y="6531880"/>
+                <a:pt x="6431699" y="6448017"/>
+                <a:pt x="6276251" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6120803" y="6577909"/>
+                <a:pt x="5788942" y="6432821"/>
+                <a:pt x="5450275" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5111608" y="6593105"/>
+                <a:pt x="4813041" y="6417852"/>
+                <a:pt x="4624300" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4435560" y="6608074"/>
+                <a:pt x="4267645" y="6449824"/>
+                <a:pt x="3920475" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3573306" y="6576102"/>
+                <a:pt x="3573462" y="6508086"/>
+                <a:pt x="3460954" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3348446" y="6517840"/>
+                <a:pt x="3173874" y="6471695"/>
+                <a:pt x="3001432" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2828990" y="6554231"/>
+                <a:pt x="2387278" y="6423747"/>
+                <a:pt x="2175457" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1963637" y="6602179"/>
+                <a:pt x="1645219" y="6463105"/>
+                <a:pt x="1349481" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1053743" y="6562821"/>
+                <a:pt x="956725" y="6475703"/>
+                <a:pt x="767808" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="578891" y="6550223"/>
+                <a:pt x="237487" y="6426278"/>
+                <a:pt x="0" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-63229" y="6233917"/>
+                <a:pt x="19309" y="6061943"/>
+                <a:pt x="0" y="5855746"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-19309" y="5649549"/>
+                <a:pt x="18633" y="5470852"/>
+                <a:pt x="0" y="5328788"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-18633" y="5186724"/>
+                <a:pt x="85385" y="4821569"/>
+                <a:pt x="0" y="4606441"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-85385" y="4391313"/>
+                <a:pt x="61801" y="4257736"/>
+                <a:pt x="0" y="4079483"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-61801" y="3901230"/>
+                <a:pt x="6158" y="3766070"/>
+                <a:pt x="0" y="3682785"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-6158" y="3599500"/>
+                <a:pt x="38688" y="3321001"/>
+                <a:pt x="0" y="3220956"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-38688" y="3120911"/>
+                <a:pt x="63501" y="2799525"/>
+                <a:pt x="0" y="2628869"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-63501" y="2458213"/>
+                <a:pt x="51876" y="2281135"/>
+                <a:pt x="0" y="1971652"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-51876" y="1662169"/>
+                <a:pt x="29215" y="1466984"/>
+                <a:pt x="0" y="1314434"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-29215" y="1161884"/>
+                <a:pt x="48423" y="946312"/>
+                <a:pt x="0" y="722347"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-48423" y="498382"/>
+                <a:pt x="34568" y="296324"/>
+                <a:pt x="0" y="0"/>
+              </a:cubicBezTo>
+              <a:close/>
+            </a:path>
+            <a:path w="12215131" h="6512963" stroke="0" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="0" y="0"/>
+              </a:moveTo>
+              <a:cubicBezTo>
+                <a:pt x="186987" y="-43043"/>
+                <a:pt x="418792" y="76070"/>
+                <a:pt x="703824" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="988856" y="-76070"/>
+                <a:pt x="896627" y="27008"/>
+                <a:pt x="1041194" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1185761" y="-27008"/>
+                <a:pt x="1301239" y="9884"/>
+                <a:pt x="1378565" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1455891" y="-9884"/>
+                <a:pt x="1632612" y="21924"/>
+                <a:pt x="1838086" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2043560" y="-21924"/>
+                <a:pt x="2093582" y="18256"/>
+                <a:pt x="2175457" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2257332" y="-18256"/>
+                <a:pt x="2393086" y="5378"/>
+                <a:pt x="2512827" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2632568" y="-5378"/>
+                <a:pt x="3064480" y="30411"/>
+                <a:pt x="3216651" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3368822" y="-30411"/>
+                <a:pt x="3590945" y="23765"/>
+                <a:pt x="3798324" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4005703" y="-23765"/>
+                <a:pt x="4404501" y="27735"/>
+                <a:pt x="4624300" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4844099" y="-27735"/>
+                <a:pt x="4765995" y="3001"/>
+                <a:pt x="4839519" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4913043" y="-3001"/>
+                <a:pt x="5192437" y="48789"/>
+                <a:pt x="5543343" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5894249" y="-48789"/>
+                <a:pt x="5657719" y="20513"/>
+                <a:pt x="5758562" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5859405" y="-20513"/>
+                <a:pt x="6006567" y="3811"/>
+                <a:pt x="6095932" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6185297" y="-3811"/>
+                <a:pt x="6724265" y="96986"/>
+                <a:pt x="6921908" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7119551" y="-96986"/>
+                <a:pt x="7177913" y="25758"/>
+                <a:pt x="7259278" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7340643" y="-25758"/>
+                <a:pt x="7422403" y="14771"/>
+                <a:pt x="7474497" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7526591" y="-14771"/>
+                <a:pt x="7620524" y="5689"/>
+                <a:pt x="7689716" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7758908" y="-5689"/>
+                <a:pt x="7932396" y="33611"/>
+                <a:pt x="8149237" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8366078" y="-33611"/>
+                <a:pt x="8623589" y="98597"/>
+                <a:pt x="8975213" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9326837" y="-98597"/>
+                <a:pt x="9404644" y="53424"/>
+                <a:pt x="9556886" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9709128" y="-53424"/>
+                <a:pt x="9746492" y="24698"/>
+                <a:pt x="9894256" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10042020" y="-24698"/>
+                <a:pt x="10272148" y="59734"/>
+                <a:pt x="10475929" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10679710" y="-59734"/>
+                <a:pt x="10961774" y="33673"/>
+                <a:pt x="11301905" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11642036" y="-33673"/>
+                <a:pt x="11462844" y="21803"/>
+                <a:pt x="11517124" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11571404" y="-21803"/>
+                <a:pt x="11941034" y="35877"/>
+                <a:pt x="12215131" y="0"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12276557" y="242823"/>
+                <a:pt x="12200072" y="353847"/>
+                <a:pt x="12215131" y="526958"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12230190" y="700069"/>
+                <a:pt x="12193326" y="871829"/>
+                <a:pt x="12215131" y="988786"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12236936" y="1105743"/>
+                <a:pt x="12213851" y="1267825"/>
+                <a:pt x="12215131" y="1515744"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12216411" y="1763663"/>
+                <a:pt x="12138895" y="1964079"/>
+                <a:pt x="12215131" y="2238091"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12291367" y="2512103"/>
+                <a:pt x="12197446" y="2507480"/>
+                <a:pt x="12215131" y="2699919"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12232816" y="2892358"/>
+                <a:pt x="12208381" y="3165933"/>
+                <a:pt x="12215131" y="3422266"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12221881" y="3678599"/>
+                <a:pt x="12210441" y="3922341"/>
+                <a:pt x="12215131" y="4144613"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12219821" y="4366885"/>
+                <a:pt x="12213420" y="4594602"/>
+                <a:pt x="12215131" y="4801830"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12216842" y="5009058"/>
+                <a:pt x="12195089" y="5191188"/>
+                <a:pt x="12215131" y="5459047"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12235173" y="5726906"/>
+                <a:pt x="12214283" y="5767415"/>
+                <a:pt x="12215131" y="5986005"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12215979" y="6204595"/>
+                <a:pt x="12191621" y="6365345"/>
+                <a:pt x="12215131" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="12060717" y="6550823"/>
+                <a:pt x="11819014" y="6469598"/>
+                <a:pt x="11633458" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="11447902" y="6556328"/>
+                <a:pt x="11051946" y="6470187"/>
+                <a:pt x="10807483" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="10563020" y="6555739"/>
+                <a:pt x="10237197" y="6422186"/>
+                <a:pt x="9981507" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9725817" y="6603740"/>
+                <a:pt x="9658727" y="6466763"/>
+                <a:pt x="9521985" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="9385243" y="6559163"/>
+                <a:pt x="9216956" y="6466056"/>
+                <a:pt x="9062464" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8907972" y="6559870"/>
+                <a:pt x="8796418" y="6497199"/>
+                <a:pt x="8725094" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8653770" y="6528727"/>
+                <a:pt x="8453989" y="6505136"/>
+                <a:pt x="8265572" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="8077155" y="6520790"/>
+                <a:pt x="7812445" y="6461099"/>
+                <a:pt x="7561748" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="7311051" y="6564827"/>
+                <a:pt x="7124174" y="6453652"/>
+                <a:pt x="6857924" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6591674" y="6572274"/>
+                <a:pt x="6652234" y="6487876"/>
+                <a:pt x="6520553" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6388872" y="6538050"/>
+                <a:pt x="6405974" y="6496854"/>
+                <a:pt x="6305334" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="6204694" y="6529072"/>
+                <a:pt x="5943409" y="6480202"/>
+                <a:pt x="5845813" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5748217" y="6545724"/>
+                <a:pt x="5676699" y="6506163"/>
+                <a:pt x="5630594" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="5584489" y="6519763"/>
+                <a:pt x="5283103" y="6460456"/>
+                <a:pt x="5048921" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4814739" y="6565470"/>
+                <a:pt x="4922544" y="6489761"/>
+                <a:pt x="4833702" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="4744860" y="6536165"/>
+                <a:pt x="4355555" y="6495571"/>
+                <a:pt x="4007726" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3659897" y="6530355"/>
+                <a:pt x="3849692" y="6499335"/>
+                <a:pt x="3792507" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3735322" y="6526591"/>
+                <a:pt x="3515626" y="6473670"/>
+                <a:pt x="3332986" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="3150346" y="6552256"/>
+                <a:pt x="2813377" y="6478781"/>
+                <a:pt x="2507010" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="2200643" y="6547145"/>
+                <a:pt x="1995472" y="6462320"/>
+                <a:pt x="1681035" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="1366599" y="6563606"/>
+                <a:pt x="1314004" y="6463784"/>
+                <a:pt x="977210" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="640417" y="6562142"/>
+                <a:pt x="204455" y="6453772"/>
+                <a:pt x="0" y="6512963"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-46582" y="6319502"/>
+                <a:pt x="16635" y="6260021"/>
+                <a:pt x="0" y="6051135"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-16635" y="5842249"/>
+                <a:pt x="4009" y="5642603"/>
+                <a:pt x="0" y="5524177"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-4009" y="5405751"/>
+                <a:pt x="54438" y="5168942"/>
+                <a:pt x="0" y="4997219"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-54438" y="4825496"/>
+                <a:pt x="5031" y="4723081"/>
+                <a:pt x="0" y="4535391"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-5031" y="4347701"/>
+                <a:pt x="44952" y="4159460"/>
+                <a:pt x="0" y="3943303"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-44952" y="3727146"/>
+                <a:pt x="58981" y="3606388"/>
+                <a:pt x="0" y="3351216"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-58981" y="3096044"/>
+                <a:pt x="5056" y="3114331"/>
+                <a:pt x="0" y="2889387"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-5056" y="2664443"/>
+                <a:pt x="75240" y="2435662"/>
+                <a:pt x="0" y="2167040"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-75240" y="1898418"/>
+                <a:pt x="36675" y="1803459"/>
+                <a:pt x="0" y="1509823"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-36675" y="1216187"/>
+                <a:pt x="10939" y="1083531"/>
+                <a:pt x="0" y="917736"/>
+              </a:cubicBezTo>
+              <a:cubicBezTo>
+                <a:pt x="-10939" y="751941"/>
+                <a:pt x="75010" y="324737"/>
+                <a:pt x="0" y="0"/>
+              </a:cubicBezTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBE5E9"/>
+        </a:solidFill>
+        <a:ln w="3175">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="sysDot"/>
+          <a:extLst>
+            <a:ext uri="{C807C97D-BFC1-408E-A445-0C87EB9F89A2}">
+              <ask:lineSketchStyleProps xmlns:ask="http://schemas.microsoft.com/office/drawing/2018/sketchyshapes" sd="3025069974">
+                <a:prstGeom prst="rect">
+                  <a:avLst/>
+                </a:prstGeom>
+                <ask:type>
+                  <ask:lineSketchScribble/>
+                </ask:type>
+              </ask:lineSketchStyleProps>
+            </a:ext>
+          </a:extLst>
+        </a:ln>
+        <a:effectLst>
+          <a:innerShdw blurRad="114300">
+            <a:prstClr val="black"/>
+          </a:innerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100">
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>155122</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>122660</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6073,16 +7070,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>154732</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>495299</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>93694</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6111,16 +7108,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>181556</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114881</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6149,16 +7146,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>152207</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>56957</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6187,19 +7184,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>433287</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>122660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>161926</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>433287</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>103610</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="City">
@@ -6222,7 +7219,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6232,8 +7229,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9258300" y="1362076"/>
-              <a:ext cx="1828800" cy="2266950"/>
+              <a:off x="433287" y="3631359"/>
+              <a:ext cx="1836964" cy="2313603"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6265,16 +7262,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>423375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>26825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>423375</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>74450</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -6310,8 +7307,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8382000" y="85725"/>
-              <a:ext cx="1828800" cy="1190625"/>
+              <a:off x="423375" y="2174810"/>
+              <a:ext cx="1836964" cy="1213951"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6341,82 +7338,316 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>294011</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>86745</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>77026</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B87F9E7-8564-92CA-83B5-FB4EDB307AE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="294011" y="281133"/>
+          <a:ext cx="6713668" cy="583163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="3200" b="1" cap="none" spc="0">
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="OCR A Extended" panose="02010509020102010303" pitchFamily="50" charset="0"/>
+            </a:rPr>
+            <a:t>E-COMMERCE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="3200" b="1" cap="none" spc="0" baseline="0">
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="OCR A Extended" panose="02010509020102010303" pitchFamily="50" charset="0"/>
+            </a:rPr>
+            <a:t> SALES DASHBOARD</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="3200" b="1" cap="none" spc="0">
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="OCR A Extended" panose="02010509020102010303" pitchFamily="50" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>408214</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>233265</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>155510</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle: Rounded Corners 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDCCCF24-B8C0-CDC4-581A-AC2130843AEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7756071" y="194388"/>
+          <a:ext cx="1662015" cy="748392"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>113522</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>55206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>550894</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>16328</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="10" name="Month">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{445F66F3-2BA1-47A7-88D1-BCBE2440939A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Month"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9286875" y="4057650"/>
-              <a:ext cx="1828800" cy="2524125"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle: Rounded Corners 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70DAB141-2333-413C-9FB0-B4F1C4FBA04F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9910665" y="249594"/>
+          <a:ext cx="1662015" cy="748392"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>567224</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>52096</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>392275</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>22937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle: Rounded Corners 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65E51A9D-6D57-4469-BA80-8E6647176A7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="567224" y="1033754"/>
+          <a:ext cx="1662015" cy="748392"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100" b="1" cap="none" spc="0">
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
             <a:solidFill>
-              <a:prstClr val="white"/>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
             </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -14323,7 +15554,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="B23:C32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -14420,8 +15651,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="10">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -14551,7 +15790,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -14648,8 +15887,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="23">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -14683,7 +15930,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -14765,8 +16012,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -14800,7 +16055,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -14870,8 +16125,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="19">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -15018,8 +16281,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -15035,7 +16306,6 @@
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{D33028C7-68A4-43A0-B516-720506AAE5EF}" sourceName="City">
   <pivotTables>
-    <pivotTable tabId="2" name="by_city"/>
     <pivotTable tabId="2" name="by cetegory"/>
     <pivotTable tabId="2" name="monthly sales"/>
     <pivotTable tabId="2" name="by product"/>
@@ -15061,7 +16331,6 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{A402FCD2-D5D0-44C5-A069-E9333FF13B22}" sourceName="Category">
   <pivotTables>
     <pivotTable tabId="2" name="by_city"/>
-    <pivotTable tabId="2" name="by cetegory"/>
     <pivotTable tabId="2" name="monthly sales"/>
     <pivotTable tabId="2" name="by product"/>
     <pivotTable tabId="2" name="top cunsumer"/>
@@ -15078,41 +16347,10 @@
 </slicerCacheDefinition>
 </file>
 
-<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{EF836BAC-2648-451C-868E-04E11FD8359F}" sourceName="Month">
-  <pivotTables>
-    <pivotTable tabId="2" name="by_city"/>
-    <pivotTable tabId="2" name="by cetegory"/>
-    <pivotTable tabId="2" name="monthly sales"/>
-    <pivotTable tabId="2" name="by product"/>
-    <pivotTable tabId="2" name="top cunsumer"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="601249990">
-      <items count="12">
-        <i x="11" s="1"/>
-        <i x="10" s="1"/>
-        <i x="0" s="1"/>
-        <i x="7" s="1"/>
-        <i x="8" s="1"/>
-        <i x="3" s="1"/>
-        <i x="5" s="1"/>
-        <i x="4" s="1"/>
-        <i x="2" s="1"/>
-        <i x="1" s="1"/>
-        <i x="9" s="1"/>
-        <i x="6" s="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="City" xr10:uid="{4A241FBB-8E34-46FC-A712-260EAC3BBC02}" cache="Slicer_City" caption="City" rowHeight="241300"/>
-  <slicer name="Category" xr10:uid="{AB868006-6975-452F-B591-E9BD8DD35C18}" cache="Slicer_Category" caption="Category" rowHeight="241300"/>
-  <slicer name="Month" xr10:uid="{44005C79-6807-4914-8C36-079DD86993E5}" cache="Slicer_Month" caption="Month" rowHeight="241300"/>
+  <slicer name="City" xr10:uid="{4A241FBB-8E34-46FC-A712-260EAC3BBC02}" cache="Slicer_City" caption="City" style="SlicerStyleLight2" rowHeight="241300"/>
+  <slicer name="Category" xr10:uid="{AB868006-6975-452F-B591-E9BD8DD35C18}" cache="Slicer_Category" caption="Category" style="SlicerStyleLight2" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -15121,7 +16359,7 @@
   <autoFilter ref="A1:L601" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{308B8AE8-0EF3-4E00-90AB-55117EA19029}" name="Order ID"/>
-    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{74135370-F89D-438A-B962-1CCD196557B1}" name="Customer Name"/>
     <tableColumn id="4" xr3:uid="{B474F51B-C2CB-4C85-A5EC-55BF075A01C9}" name="City"/>
     <tableColumn id="5" xr3:uid="{4939F22B-CA78-4718-98BD-CCB69768D3E0}" name="Product Name"/>
@@ -15129,8 +16367,8 @@
     <tableColumn id="7" xr3:uid="{6A004A32-99E0-4D3A-9463-C6C5B5320FE6}" name="Quantity"/>
     <tableColumn id="8" xr3:uid="{43C25B3C-200A-4AAC-B496-82A33D7E64F3}" name="Price"/>
     <tableColumn id="9" xr3:uid="{70B3244E-87E1-402D-A7F5-E4AC16E54570}" name="Total Sales"/>
-    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="26">
       <calculatedColumnFormula>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{B0A5E0C2-382B-4A6A-89AF-DDA7D4F97E39}" name="Profit"/>
@@ -15428,7 +16666,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
@@ -15441,7 +16679,7 @@
       <c r="B3" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>353</v>
       </c>
     </row>
@@ -15449,7 +16687,7 @@
       <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="5">
         <v>1385000</v>
       </c>
     </row>
@@ -15457,7 +16695,7 @@
       <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="5">
         <v>16567500</v>
       </c>
     </row>
@@ -15465,7 +16703,7 @@
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="5">
         <v>1205600</v>
       </c>
     </row>
@@ -15473,7 +16711,7 @@
       <c r="B7" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="5">
         <v>19158100</v>
       </c>
     </row>
@@ -15481,7 +16719,7 @@
       <c r="B11" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>353</v>
       </c>
     </row>
@@ -15489,7 +16727,7 @@
       <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="5">
         <v>2737200</v>
       </c>
     </row>
@@ -15497,7 +16735,7 @@
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="5">
         <v>2996300</v>
       </c>
     </row>
@@ -15505,7 +16743,7 @@
       <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="5">
         <v>1914000</v>
       </c>
     </row>
@@ -15513,7 +16751,7 @@
       <c r="B15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="5">
         <v>3072800</v>
       </c>
     </row>
@@ -15521,7 +16759,7 @@
       <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="5">
         <v>2920500</v>
       </c>
     </row>
@@ -15529,7 +16767,7 @@
       <c r="B17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="5">
         <v>2604000</v>
       </c>
     </row>
@@ -15537,7 +16775,7 @@
       <c r="B18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="5">
         <v>2913300</v>
       </c>
     </row>
@@ -15545,7 +16783,7 @@
       <c r="B19" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="5">
         <v>19158100</v>
       </c>
     </row>
@@ -15553,7 +16791,7 @@
       <c r="B23" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>353</v>
       </c>
     </row>
@@ -15561,7 +16799,7 @@
       <c r="B24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="5">
         <v>315000</v>
       </c>
     </row>
@@ -15569,7 +16807,7 @@
       <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="5">
         <v>587500</v>
       </c>
     </row>
@@ -15577,7 +16815,7 @@
       <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="5">
         <v>414000</v>
       </c>
     </row>
@@ -15585,7 +16823,7 @@
       <c r="B27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="5">
         <v>11400000</v>
       </c>
     </row>
@@ -15593,7 +16831,7 @@
       <c r="B28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="5">
         <v>4580000</v>
       </c>
     </row>
@@ -15601,7 +16839,7 @@
       <c r="B29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="5">
         <v>606000</v>
       </c>
     </row>
@@ -15609,7 +16847,7 @@
       <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="5">
         <v>185600</v>
       </c>
     </row>
@@ -15617,7 +16855,7 @@
       <c r="B31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="5">
         <v>1070000</v>
       </c>
     </row>
@@ -15625,7 +16863,7 @@
       <c r="B32" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="5">
         <v>19158100</v>
       </c>
     </row>
@@ -15633,7 +16871,7 @@
       <c r="B36" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="5" t="s">
         <v>353</v>
       </c>
     </row>
@@ -15641,7 +16879,7 @@
       <c r="B37" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="5">
         <v>2075900</v>
       </c>
     </row>
@@ -15649,7 +16887,7 @@
       <c r="B38" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="5">
         <v>1004500</v>
       </c>
     </row>
@@ -15657,7 +16895,7 @@
       <c r="B39" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="5">
         <v>1088700</v>
       </c>
     </row>
@@ -15665,7 +16903,7 @@
       <c r="B40" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="5">
         <v>1215100</v>
       </c>
     </row>
@@ -15673,7 +16911,7 @@
       <c r="B41" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="5">
         <v>1553100</v>
       </c>
     </row>
@@ -15681,7 +16919,7 @@
       <c r="B42" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="5">
         <v>2927200</v>
       </c>
     </row>
@@ -15689,7 +16927,7 @@
       <c r="B43" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="5">
         <v>1340000</v>
       </c>
     </row>
@@ -15697,7 +16935,7 @@
       <c r="B44" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="5">
         <v>1671200</v>
       </c>
     </row>
@@ -15705,7 +16943,7 @@
       <c r="B45" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="5">
         <v>1662900</v>
       </c>
     </row>
@@ -15713,7 +16951,7 @@
       <c r="B46" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="5">
         <v>1699400</v>
       </c>
     </row>
@@ -15721,7 +16959,7 @@
       <c r="B47" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="5">
         <v>1319900</v>
       </c>
     </row>
@@ -15729,7 +16967,7 @@
       <c r="B48" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="5">
         <v>1600200</v>
       </c>
     </row>
@@ -15737,7 +16975,7 @@
       <c r="B49" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="5">
         <v>19158100</v>
       </c>
     </row>
@@ -15745,7 +16983,7 @@
       <c r="B53" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="5" t="s">
         <v>353</v>
       </c>
     </row>
@@ -15753,7 +16991,7 @@
       <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="5">
         <v>749900</v>
       </c>
     </row>
@@ -15761,7 +16999,7 @@
       <c r="B55" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="5">
         <v>1526900</v>
       </c>
     </row>
@@ -15769,7 +17007,7 @@
       <c r="B56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="5">
         <v>1139000</v>
       </c>
     </row>
@@ -15777,7 +17015,7 @@
       <c r="B57" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="5">
         <v>2066300</v>
       </c>
     </row>
@@ -15785,7 +17023,7 @@
       <c r="B58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="5">
         <v>1121800</v>
       </c>
     </row>
@@ -15793,7 +17031,7 @@
       <c r="B59" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="5">
         <v>2391600</v>
       </c>
     </row>
@@ -15801,7 +17039,7 @@
       <c r="B60" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="5">
         <v>1752800</v>
       </c>
     </row>
@@ -15809,7 +17047,7 @@
       <c r="B61" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="5">
         <v>934900</v>
       </c>
     </row>
@@ -15817,7 +17055,7 @@
       <c r="B62" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="5">
         <v>1588100</v>
       </c>
     </row>
@@ -15825,7 +17063,7 @@
       <c r="B63" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="5">
         <v>3068200</v>
       </c>
     </row>
@@ -15833,7 +17071,7 @@
       <c r="B64" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="5">
         <v>1144000</v>
       </c>
     </row>
@@ -15841,7 +17079,7 @@
       <c r="B65" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="5">
         <v>1674600</v>
       </c>
     </row>
@@ -15849,7 +17087,7 @@
       <c r="B66" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="5">
         <v>19158100</v>
       </c>
     </row>
@@ -15860,54 +17098,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB32EC35-6A1C-458D-980E-B380654E859D}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
-        <f>SUM(Ecommerce_Data[Total Sales])</f>
-        <v>19158100</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="F3" s="6">
-        <f>COUNTA(Ecommerce_Data[Order ID])</f>
-        <v>600</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="J3" s="6">
-        <f>SUM(Ecommerce_Data[Quantity])</f>
-        <v>1757</v>
-      </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-    </row>
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="J3:K4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -15971,7 +17170,7 @@
         <v>349</v>
       </c>
       <c r="L1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481C162B-5B4E-4192-8177-820794BAAB22}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8859D242-7F0C-422A-A63B-26D5A2901C50}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3069" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3074" uniqueCount="372">
   <si>
     <t>Order ID</t>
   </si>
@@ -1151,14 +1151,30 @@
   <si>
     <t>Profit</t>
   </si>
+  <si>
+    <t>total sales</t>
+  </si>
+  <si>
+    <t>total oder</t>
+  </si>
+  <si>
+    <t>total customers</t>
+  </si>
+  <si>
+    <t>average oder value</t>
+  </si>
+  <si>
+    <t>total qauntity sold</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="175" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1195,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1204,6 +1220,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7471,7 +7488,7 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>155510</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="Pivots!F7">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12" name="Rectangle: Rounded Corners 11">
           <a:extLst>
@@ -7493,18 +7510,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+          <a:schemeClr val="dk1"/>
         </a:lnRef>
         <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -7512,7 +7527,50 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-IN" sz="1100"/>
+          <a:fld id="{3E95F172-B225-4BEC-A0C8-ED248710CDE6}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>600</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-IN" sz="1100" b="1" cap="none" spc="0">
+            <a:ln/>
+            <a:pattFill prst="dkUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7531,7 +7589,7 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>16328</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="Pivots!F13">
       <xdr:nvSpPr>
         <xdr:cNvPr id="13" name="Rectangle: Rounded Corners 12">
           <a:extLst>
@@ -7572,6 +7630,17 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:fld id="{9FA46A48-A744-4263-82AD-2456137FCBC3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>31930.16667</a:t>
+          </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -7581,17 +7650,17 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>567224</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>52096</xdr:rowOff>
+      <xdr:colOff>372837</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>178448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>392275</xdr:colOff>
+      <xdr:colOff>398496</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>22937</xdr:rowOff>
+      <xdr:rowOff>19439</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="Pivots!F4">
       <xdr:nvSpPr>
         <xdr:cNvPr id="14" name="Rectangle: Rounded Corners 13">
           <a:extLst>
@@ -7604,8 +7673,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="567224" y="1033754"/>
-          <a:ext cx="1662015" cy="748392"/>
+          <a:off x="372837" y="965718"/>
+          <a:ext cx="1862623" cy="812930"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7626,24 +7695,198 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Revenue</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:fld id="{C62A7678-75DF-4085-9E33-38D8B37BAF7D}" type="TxLink">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr algn="ctr"/>
+            <a:t> ₹ 19,158,100 </a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-IN" sz="1800" b="1" cap="none" spc="0">
+            <a:ln/>
+            <a:pattFill prst="dkUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>103802</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>191278</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>541174</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="Pivots!F16">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle: Rounded Corners 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F6883D-720C-422F-967A-EDD99DB2DAE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5614695" y="774441"/>
+          <a:ext cx="1662015" cy="748392"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:fld id="{BCFA1E5C-254E-4FCC-8BA6-4D5F74777122}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>1757</a:t>
+          </a:fld>
           <a:endParaRPr lang="en-IN" sz="1100" b="1" cap="none" spc="0">
-            <a:ln w="22225">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:effectLst/>
+            <a:ln/>
+            <a:pattFill prst="dkUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -16662,7 +16905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF3CD5B-B6B3-48EA-8FE8-F51E21FA5F4E}">
-  <dimension ref="B3:C66"/>
+  <dimension ref="B3:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -16675,23 +16918,30 @@
     <col min="12" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>351</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="5">
         <v>1385000</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F4" s="6">
+        <f>SUM(Ecommerce_Data[Total Sales])</f>
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
@@ -16699,23 +16949,35 @@
         <v>16567500</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="5">
         <v>1205600</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C7" s="5">
         <v>19158100</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f>COUNTA(Ecommerce_Data[Order ID])</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>351</v>
       </c>
@@ -16723,23 +16985,30 @@
         <v>353</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="5">
         <v>2737200</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="5">
         <v>2996300</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f>SUM(Ecommerce_Data[Total Sales]) / COUNTA(Ecommerce_Data[Order ID])</f>
+        <v>31930.166666666668</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
@@ -16747,20 +17016,27 @@
         <v>1914000</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="5">
         <v>3072800</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="5">
         <v>2920500</v>
+      </c>
+      <c r="F16">
+        <f>SUM(Ecommerce_Data[Quantity])</f>
+        <v>1757</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8859D242-7F0C-422A-A63B-26D5A2901C50}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2564AD-456C-4F9A-9C92-EB17404A6467}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1173,8 +1173,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="175" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0_ ;_ [$₹-4009]\ * \-#,##0_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1219,91 +1219,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1312,6 +1234,36 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1455,8 +1407,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1497,6 +1448,64 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:shade val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="25000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="25000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:tint val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="25000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1536,6 +1545,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F5A5-47A6-B74B-D72BBB258F0A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1555,6 +1569,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F5A5-47A6-B74B-D72BBB258F0A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1576,6 +1595,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F5A5-47A6-B74B-D72BBB258F0A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2438,17 +2462,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2481,7 +2495,6 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2602,7 +2615,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2922,8 +2934,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2973,10 +2984,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent2">
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -2989,7 +3000,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -2999,10 +3010,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent4">
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3015,7 +3026,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3025,10 +3036,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent5"/>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent5">
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3041,7 +3052,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent5"/>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3077,10 +3088,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent3">
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3093,7 +3104,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3103,10 +3114,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent6"/>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent6">
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3119,7 +3130,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent6"/>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3129,13 +3140,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
               <a:schemeClr val="accent1">
-                <a:lumMod val="60000"/>
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3148,9 +3156,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3160,13 +3166,10 @@
         <c:spPr>
           <a:pattFill prst="ltUpDiag">
             <a:fgClr>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:fgClr>
             <a:bgClr>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
+              <a:schemeClr val="accent1">
                 <a:lumMod val="20000"/>
                 <a:lumOff val="80000"/>
               </a:schemeClr>
@@ -3179,9 +3182,7 @@
           </a:ln>
           <a:effectLst>
             <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:innerShdw>
           </a:effectLst>
         </c:spPr>
@@ -3503,6 +3504,11 @@
                 </a:innerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-4531-4B8B-B702-CB92D574AEB0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -7202,15 +7208,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>433287</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>122660</xdr:rowOff>
+      <xdr:colOff>452725</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>132380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>433287</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>103610</xdr:rowOff>
+      <xdr:colOff>398494</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>106910</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7246,8 +7252,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="433287" y="3631359"/>
-              <a:ext cx="1836964" cy="2313603"/>
+              <a:off x="452725" y="4029854"/>
+              <a:ext cx="1782733" cy="2307184"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7281,14 +7287,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>423375</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>26825</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7379</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>423375</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>74450</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>55004</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7324,7 +7330,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="423375" y="2174810"/>
+              <a:off x="423375" y="2738527"/>
               <a:ext cx="1836964" cy="1213951"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7478,15 +7484,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>408214</xdr:colOff>
+      <xdr:colOff>398495</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>48596</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>233265</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>155510</xdr:rowOff>
+      <xdr:colOff>223546</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9718</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Pivots!F7">
       <xdr:nvSpPr>
@@ -7501,7 +7507,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7756071" y="194388"/>
+          <a:off x="7746352" y="242984"/>
           <a:ext cx="1662015" cy="748392"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -7510,29 +7516,39 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="accent1"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:fld id="{3E95F172-B225-4BEC-A0C8-ED248710CDE6}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0">
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
               <a:ln/>
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:effectLst>
                 <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
                   <a:schemeClr val="dk1">
@@ -7545,9 +7561,43 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:t>Total Oder</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:fld id="{3E95F172-B225-4BEC-A0C8-ED248710CDE6}" type="TxLink">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>600</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-IN" sz="1100" b="1" cap="none" spc="0">
+          <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
             <a:pattFill prst="dkUpDiag">
               <a:fgClr>
@@ -7570,6 +7620,9 @@
                 </a:schemeClr>
               </a:outerShdw>
             </a:effectLst>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7579,15 +7632,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>113522</xdr:colOff>
+      <xdr:colOff>55206</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55206</xdr:rowOff>
+      <xdr:rowOff>35767</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>550894</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>16328</xdr:rowOff>
+      <xdr:colOff>492578</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>191277</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Pivots!F13">
       <xdr:nvSpPr>
@@ -7602,7 +7655,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9910665" y="249594"/>
+          <a:off x="9852349" y="230155"/>
           <a:ext cx="1662015" cy="748392"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -7611,37 +7664,114 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+          <a:schemeClr val="accent1"/>
         </a:lnRef>
         <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
           <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:fld id="{9FA46A48-A744-4263-82AD-2456137FCBC3}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:t> Oder  Value</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:fld id="{9FA46A48-A744-4263-82AD-2456137FCBC3}" type="TxLink">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>31930.16667</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-IN" sz="1100"/>
+          <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+            <a:ln/>
+            <a:pattFill prst="dkUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:effectLst>
+              <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7794,16 +7924,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>103802</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>191278</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>369335</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>113519</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>541174</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>397747</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>149784</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Pivots!F16">
       <xdr:nvSpPr>
@@ -7818,8 +7948,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5614695" y="774441"/>
-          <a:ext cx="1662015" cy="748392"/>
+          <a:off x="369335" y="1872728"/>
+          <a:ext cx="1865376" cy="813816"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7827,29 +7957,39 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="accent1"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="accent1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:fld id="{BCFA1E5C-254E-4FCC-8BA6-4D5F74777122}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0">
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
               <a:ln/>
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
               <a:effectLst>
                 <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
                   <a:schemeClr val="dk1">
@@ -7862,9 +8002,43 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:t>Quantity Sold</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:fld id="{BCFA1E5C-254E-4FCC-8BA6-4D5F74777122}" type="TxLink">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+              <a:ln/>
+              <a:pattFill prst="dkUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>1757</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-IN" sz="1100" b="1" cap="none" spc="0">
+          <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
             <a:pattFill prst="dkUpDiag">
               <a:fgClr>
@@ -7887,6 +8061,9 @@
                 </a:schemeClr>
               </a:outerShdw>
             </a:effectLst>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -15797,6 +15974,556 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="6">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="top cunsumer" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B53:C66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="8"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="B23:C32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -15894,13 +16621,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="25">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16032,520 +16759,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="23">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="19">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="top cunsumer" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B53:C66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="8"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="167"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="17">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{D33028C7-68A4-43A0-B516-720506AAE5EF}" sourceName="City">
   <pivotTables>
@@ -16602,7 +16815,7 @@
   <autoFilter ref="A1:L601" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{308B8AE8-0EF3-4E00-90AB-55117EA19029}" name="Order ID"/>
-    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{74135370-F89D-438A-B962-1CCD196557B1}" name="Customer Name"/>
     <tableColumn id="4" xr3:uid="{B474F51B-C2CB-4C85-A5EC-55BF075A01C9}" name="City"/>
     <tableColumn id="5" xr3:uid="{4939F22B-CA78-4718-98BD-CCB69768D3E0}" name="Product Name"/>
@@ -16610,8 +16823,8 @@
     <tableColumn id="7" xr3:uid="{6A004A32-99E0-4D3A-9463-C6C5B5320FE6}" name="Quantity"/>
     <tableColumn id="8" xr3:uid="{43C25B3C-200A-4AAC-B496-82A33D7E64F3}" name="Price"/>
     <tableColumn id="9" xr3:uid="{70B3244E-87E1-402D-A7F5-E4AC16E54570}" name="Total Sales"/>
-    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="27"/>
-    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="26">
+    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="0">
       <calculatedColumnFormula>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{B0A5E0C2-382B-4A6A-89AF-DDA7D4F97E39}" name="Profit"/>

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2564AD-456C-4F9A-9C92-EB17404A6467}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F19A08-2261-4E82-B6D0-2428290524EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivots" sheetId="2" r:id="rId1"/>
@@ -1211,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1221,11 +1221,132 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="53">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -7056,15 +7177,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
+      <xdr:colOff>226462</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>155122</xdr:rowOff>
+      <xdr:rowOff>96809</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>320741</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>122660</xdr:rowOff>
+      <xdr:rowOff>19442</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7093,16 +7214,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>590549</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>17104</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>154732</xdr:rowOff>
+      <xdr:rowOff>115856</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
+      <xdr:colOff>277000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>93694</xdr:rowOff>
+      <xdr:rowOff>54818</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7132,15 +7253,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>181556</xdr:rowOff>
+      <xdr:colOff>178840</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>142679</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>330462</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>114881</xdr:rowOff>
+      <xdr:rowOff>87475</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7172,13 +7293,13 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>152207</xdr:rowOff>
+      <xdr:rowOff>93893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>56957</xdr:rowOff>
+      <xdr:colOff>252704</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>165230</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7516,13 +7637,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -7595,7 +7716,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>600</a:t>
+            <a:t>601</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
@@ -7664,13 +7785,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -7743,7 +7864,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>31930.16667</a:t>
+            <a:t>31877.03827</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
@@ -7780,15 +7901,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>372837</xdr:colOff>
+      <xdr:colOff>421432</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>178448</xdr:rowOff>
+      <xdr:rowOff>100696</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>398496</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19439</xdr:rowOff>
+      <xdr:colOff>447091</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>136075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Pivots!F4">
       <xdr:nvSpPr>
@@ -7803,7 +7924,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="372837" y="965718"/>
+          <a:off x="421432" y="887966"/>
           <a:ext cx="1862623" cy="812930"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -7812,13 +7933,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -7925,15 +8046,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>369335</xdr:colOff>
+      <xdr:colOff>408211</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>113519</xdr:rowOff>
+      <xdr:rowOff>45486</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>397747</xdr:colOff>
+      <xdr:colOff>436623</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>149784</xdr:rowOff>
+      <xdr:rowOff>81751</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Pivots!F16">
       <xdr:nvSpPr>
@@ -7948,7 +8069,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="369335" y="1872728"/>
+          <a:off x="408211" y="1804695"/>
           <a:ext cx="1865376" cy="813816"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -7957,13 +8078,13 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:lnRef>
         <a:fillRef idx="1">
           <a:schemeClr val="lt1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent5"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="dk1"/>
@@ -16074,10 +16195,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="4">
+    <format dxfId="44">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16199,10 +16320,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="6">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16312,10 +16433,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="8">
+    <format dxfId="48">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16504,10 +16625,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="10">
+    <format dxfId="50">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16624,10 +16745,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="12">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16811,11 +16932,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}" name="Ecommerce_Data" displayName="Ecommerce_Data" ref="A1:L601" totalsRowShown="0">
-  <autoFilter ref="A1:L601" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}" name="Ecommerce_Data" displayName="Ecommerce_Data" ref="A1:L602" totalsRowShown="0">
+  <autoFilter ref="A1:L602" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{308B8AE8-0EF3-4E00-90AB-55117EA19029}" name="Order ID"/>
-    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="42"/>
     <tableColumn id="3" xr3:uid="{74135370-F89D-438A-B962-1CCD196557B1}" name="Customer Name"/>
     <tableColumn id="4" xr3:uid="{B474F51B-C2CB-4C85-A5EC-55BF075A01C9}" name="City"/>
     <tableColumn id="5" xr3:uid="{4939F22B-CA78-4718-98BD-CCB69768D3E0}" name="Product Name"/>
@@ -16823,8 +16944,8 @@
     <tableColumn id="7" xr3:uid="{6A004A32-99E0-4D3A-9463-C6C5B5320FE6}" name="Quantity"/>
     <tableColumn id="8" xr3:uid="{43C25B3C-200A-4AAC-B496-82A33D7E64F3}" name="Price"/>
     <tableColumn id="9" xr3:uid="{70B3244E-87E1-402D-A7F5-E4AC16E54570}" name="Total Sales"/>
-    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="41"/>
+    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="40">
       <calculatedColumnFormula>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{B0A5E0C2-382B-4A6A-89AF-DDA7D4F97E39}" name="Profit"/>
@@ -17182,7 +17303,7 @@
       </c>
       <c r="F7">
         <f>COUNTA(Ecommerce_Data[Order ID])</f>
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -17218,7 +17339,7 @@
       </c>
       <c r="F13">
         <f>SUM(Ecommerce_Data[Total Sales]) / COUNTA(Ecommerce_Data[Order ID])</f>
-        <v>31930.166666666668</v>
+        <v>31877.038269550751</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
@@ -17611,7 +17732,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L601"/>
+  <dimension ref="A1:L602"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -39862,6 +39983,16 @@
         <v>Oct</v>
       </c>
     </row>
+    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A602">
+        <v>1601</v>
+      </c>
+      <c r="J602" s="2"/>
+      <c r="K602" s="7" t="str">
+        <f>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</f>
+        <v>Jan</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ecommerce_dataset.xlsx
+++ b/ecommerce_dataset.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38434b598a5cd0be/Desktop/e-Commerce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F19A08-2261-4E82-B6D0-2428290524EF}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_C8A876209441D2CEEB3B98154B5DCE3A0742A5AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9A964D-A22E-4D08-82BA-0E884B00F13E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pivots" sheetId="2" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="4" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="4" r:id="rId1"/>
+    <sheet name="Pivots" sheetId="2" r:id="rId2"/>
     <sheet name="Ecommerce_Data" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="184" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1221,12 +1221,726 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="291">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
@@ -7339,8 +8053,8 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>106910</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="City">
@@ -7363,7 +8077,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7417,8 +8131,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>55004</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Category">
@@ -7441,7 +8155,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7654,40 +8368,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
-              <a:ln/>
-              <a:pattFill prst="dkUpDiag">
-                <a:fgClr>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:fgClr>
-                <a:bgClr>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:bgClr>
-              </a:pattFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:alpha val="40000"/>
-                  </a:schemeClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Total Oder</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:fld id="{3E95F172-B225-4BEC-A0C8-ED248710CDE6}" type="TxLink">
+          <a:fld id="{29B7A57C-D255-4297-BF0A-E13E3BDC0947}" type="TxLink">
             <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
               <a:ln/>
               <a:pattFill prst="dkUpDiag">
@@ -7716,7 +8397,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>601</a:t>
+            <a:t>Total Oder 600</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
@@ -7802,40 +8483,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
-              <a:ln/>
-              <a:pattFill prst="dkUpDiag">
-                <a:fgClr>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:fgClr>
-                <a:bgClr>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:bgClr>
-              </a:pattFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:alpha val="40000"/>
-                  </a:schemeClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-            </a:rPr>
-            <a:t> Oder  Value</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:fld id="{9FA46A48-A744-4263-82AD-2456137FCBC3}" type="TxLink">
+          <a:fld id="{A83276A8-3F9D-408D-9CC3-A71966BFAC05}" type="TxLink">
             <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
               <a:ln/>
               <a:pattFill prst="dkUpDiag">
@@ -7864,7 +8512,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>31877.03827</a:t>
+            <a:t>Oder Value 31930.1666666667</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
             <a:ln/>
@@ -8195,11 +8843,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="admin" refreshedDate="46114.503368287034" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="600" xr:uid="{C8251FCF-0D02-4679-8221-8792DFBC8E87}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="admin" refreshedDate="46126.736950810184" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="600" xr:uid="{C8251FCF-0D02-4679-8221-8792DFBC8E87}">
   <cacheSource type="worksheet">
     <worksheetSource name="Ecommerce_Data"/>
   </cacheSource>
-  <cacheFields count="11">
+  <cacheFields count="12">
     <cacheField name="Order ID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1600"/>
     </cacheField>
@@ -8207,7 +8855,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Customer Name" numFmtId="0">
-      <sharedItems count="12">
+      <sharedItems containsBlank="1" count="13">
         <s v="Neha"/>
         <s v="Rohit"/>
         <s v="Raj"/>
@@ -8220,10 +8868,11 @@
         <s v="Pooja"/>
         <s v="Anjali"/>
         <s v="Sahil"/>
+        <m u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="City" numFmtId="0">
-      <sharedItems count="7">
+      <sharedItems containsBlank="1" count="8">
         <s v="Mumbai"/>
         <s v="Delhi"/>
         <s v="Surat"/>
@@ -8231,10 +8880,11 @@
         <s v="Jaipur"/>
         <s v="Ahmedabad"/>
         <s v="Pune"/>
+        <m u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Product Name" numFmtId="0">
-      <sharedItems count="8">
+      <sharedItems containsBlank="1" count="9">
         <s v="T-Shirt"/>
         <s v="Shoes"/>
         <s v="Laptop"/>
@@ -8243,13 +8893,15 @@
         <s v="Bag"/>
         <s v="Watch"/>
         <s v="Jeans"/>
+        <m u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
-      <sharedItems count="3">
+      <sharedItems containsBlank="1" count="4">
         <s v="Fashion"/>
         <s v="Electronics"/>
         <s v="Accessories"/>
+        <m u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Quantity" numFmtId="0">
@@ -8265,7 +8917,7 @@
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
     </cacheField>
     <cacheField name="Month" numFmtId="0">
-      <sharedItems count="12">
+      <sharedItems containsBlank="1" count="13">
         <s v="Mar"/>
         <s v="Oct"/>
         <s v="Sep"/>
@@ -8278,7 +8930,11 @@
         <s v="Nov"/>
         <s v="Feb"/>
         <s v="Jan"/>
+        <m u="1"/>
       </sharedItems>
+    </cacheField>
+    <cacheField name="Profit" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -8303,6 +8959,7 @@
     <n v="2400"/>
     <d v="2024-03-02T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1002"/>
@@ -8316,6 +8973,7 @@
     <n v="6000"/>
     <d v="2024-10-09T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1003"/>
@@ -8329,6 +8987,7 @@
     <n v="100000"/>
     <d v="2024-10-02T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1004"/>
@@ -8342,6 +9001,7 @@
     <n v="2500"/>
     <d v="2024-09-28T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1005"/>
@@ -8355,6 +9015,7 @@
     <n v="100000"/>
     <d v="2024-06-22T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1006"/>
@@ -8368,6 +9029,7 @@
     <n v="3000"/>
     <d v="2024-08-15T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1007"/>
@@ -8381,6 +9043,7 @@
     <n v="250000"/>
     <d v="2024-07-13T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1008"/>
@@ -8394,6 +9057,7 @@
     <n v="60000"/>
     <d v="2024-03-04T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1009"/>
@@ -8407,6 +9071,7 @@
     <n v="12000"/>
     <d v="2024-12-01T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1010"/>
@@ -8420,6 +9085,7 @@
     <n v="50000"/>
     <d v="2024-04-26T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1011"/>
@@ -8433,6 +9099,7 @@
     <n v="5000"/>
     <d v="2024-10-18T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1012"/>
@@ -8446,6 +9113,7 @@
     <n v="7500"/>
     <d v="2024-05-13T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1013"/>
@@ -8459,6 +9127,7 @@
     <n v="6000"/>
     <d v="2024-04-26T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1014"/>
@@ -8472,6 +9141,7 @@
     <n v="3200"/>
     <d v="2024-10-06T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1015"/>
@@ -8485,6 +9155,7 @@
     <n v="25000"/>
     <d v="2024-11-06T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1016"/>
@@ -8498,6 +9169,7 @@
     <n v="6000"/>
     <d v="2024-08-01T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1017"/>
@@ -8511,6 +9183,7 @@
     <n v="5000"/>
     <d v="2024-04-12T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1018"/>
@@ -8524,6 +9197,7 @@
     <n v="20000"/>
     <d v="2024-03-05T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1019"/>
@@ -8537,6 +9211,7 @@
     <n v="20000"/>
     <d v="2024-02-12T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1020"/>
@@ -8550,6 +9225,7 @@
     <n v="12500"/>
     <d v="2024-02-14T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1021"/>
@@ -8563,6 +9239,7 @@
     <n v="200000"/>
     <d v="2024-04-25T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1022"/>
@@ -8576,6 +9253,7 @@
     <n v="6000"/>
     <d v="2024-12-25T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1023"/>
@@ -8589,6 +9267,7 @@
     <n v="12000"/>
     <d v="2024-10-15T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1024"/>
@@ -8602,6 +9281,7 @@
     <n v="2000"/>
     <d v="2024-06-29T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1025"/>
@@ -8615,6 +9295,7 @@
     <n v="80000"/>
     <d v="2024-01-30T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1026"/>
@@ -8628,6 +9309,7 @@
     <n v="6000"/>
     <d v="2024-06-16T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1027"/>
@@ -8641,6 +9323,7 @@
     <n v="4500"/>
     <d v="2024-09-02T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1028"/>
@@ -8654,6 +9337,7 @@
     <n v="20000"/>
     <d v="2024-08-25T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1029"/>
@@ -8667,6 +9351,7 @@
     <n v="60000"/>
     <d v="2024-10-03T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1030"/>
@@ -8680,6 +9365,7 @@
     <n v="3000"/>
     <d v="2024-09-15T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1031"/>
@@ -8693,6 +9379,7 @@
     <n v="1600"/>
     <d v="2024-02-10T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1032"/>
@@ -8706,6 +9393,7 @@
     <n v="40000"/>
     <d v="2024-06-24T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1033"/>
@@ -8719,6 +9407,7 @@
     <n v="25000"/>
     <d v="2024-09-03T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1034"/>
@@ -8732,6 +9421,7 @@
     <n v="1600"/>
     <d v="2024-04-25T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1035"/>
@@ -8745,6 +9435,7 @@
     <n v="2500"/>
     <d v="2024-12-18T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1036"/>
@@ -8758,6 +9449,7 @@
     <n v="20000"/>
     <d v="2024-04-29T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1037"/>
@@ -8771,6 +9463,7 @@
     <n v="15000"/>
     <d v="2024-09-24T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1038"/>
@@ -8784,6 +9477,7 @@
     <n v="10000"/>
     <d v="2024-11-12T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1039"/>
@@ -8797,6 +9491,7 @@
     <n v="200000"/>
     <d v="2024-09-17T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1040"/>
@@ -8810,6 +9505,7 @@
     <n v="250000"/>
     <d v="2024-01-22T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1041"/>
@@ -8823,6 +9519,7 @@
     <n v="2500"/>
     <d v="2024-08-02T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1042"/>
@@ -8836,6 +9533,7 @@
     <n v="3200"/>
     <d v="2024-02-16T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1043"/>
@@ -8849,6 +9547,7 @@
     <n v="4000"/>
     <d v="2024-10-01T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1044"/>
@@ -8862,6 +9561,7 @@
     <n v="20000"/>
     <d v="2024-12-02T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1045"/>
@@ -8875,6 +9575,7 @@
     <n v="50000"/>
     <d v="2024-06-06T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1046"/>
@@ -8888,6 +9589,7 @@
     <n v="10000"/>
     <d v="2024-08-10T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1047"/>
@@ -8901,6 +9603,7 @@
     <n v="12000"/>
     <d v="2024-11-05T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1048"/>
@@ -8914,6 +9617,7 @@
     <n v="4000"/>
     <d v="2024-11-25T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1049"/>
@@ -8927,6 +9631,7 @@
     <n v="4500"/>
     <d v="2024-11-04T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1050"/>
@@ -8940,6 +9645,7 @@
     <n v="1600"/>
     <d v="2024-10-14T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1051"/>
@@ -8953,6 +9659,7 @@
     <n v="20000"/>
     <d v="2024-03-01T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1052"/>
@@ -8966,6 +9673,7 @@
     <n v="8000"/>
     <d v="2024-12-21T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1053"/>
@@ -8979,6 +9687,7 @@
     <n v="800"/>
     <d v="2024-05-24T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1054"/>
@@ -8992,6 +9701,7 @@
     <n v="80000"/>
     <d v="2024-06-02T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1055"/>
@@ -9005,6 +9715,7 @@
     <n v="15000"/>
     <d v="2024-01-18T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1056"/>
@@ -9018,6 +9729,7 @@
     <n v="250000"/>
     <d v="2024-04-23T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1057"/>
@@ -9031,6 +9743,7 @@
     <n v="6000"/>
     <d v="2024-04-22T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1058"/>
@@ -9044,6 +9757,7 @@
     <n v="20000"/>
     <d v="2024-09-18T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1059"/>
@@ -9057,6 +9771,7 @@
     <n v="6000"/>
     <d v="2024-10-09T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1060"/>
@@ -9070,6 +9785,7 @@
     <n v="10000"/>
     <d v="2024-09-10T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1061"/>
@@ -9083,6 +9799,7 @@
     <n v="6000"/>
     <d v="2024-10-06T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1062"/>
@@ -9096,6 +9813,7 @@
     <n v="7500"/>
     <d v="2024-12-22T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1063"/>
@@ -9109,6 +9827,7 @@
     <n v="100000"/>
     <d v="2024-01-20T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1064"/>
@@ -9122,6 +9841,7 @@
     <n v="20000"/>
     <d v="2024-06-08T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1065"/>
@@ -9135,6 +9855,7 @@
     <n v="3000"/>
     <d v="2024-02-01T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1066"/>
@@ -9148,6 +9869,7 @@
     <n v="7500"/>
     <d v="2024-04-13T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1067"/>
@@ -9161,6 +9883,7 @@
     <n v="200000"/>
     <d v="2024-09-29T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1068"/>
@@ -9174,6 +9897,7 @@
     <n v="8000"/>
     <d v="2024-12-30T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1069"/>
@@ -9187,6 +9911,7 @@
     <n v="150000"/>
     <d v="2024-12-05T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1070"/>
@@ -9200,6 +9925,7 @@
     <n v="12500"/>
     <d v="2024-09-05T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1071"/>
@@ -9213,6 +9939,7 @@
     <n v="6000"/>
     <d v="2024-06-18T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1072"/>
@@ -9226,6 +9953,7 @@
     <n v="6000"/>
     <d v="2024-03-05T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1073"/>
@@ -9239,6 +9967,7 @@
     <n v="8000"/>
     <d v="2024-02-04T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1074"/>
@@ -9252,6 +9981,7 @@
     <n v="3000"/>
     <d v="2024-01-30T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1075"/>
@@ -9265,6 +9995,7 @@
     <n v="20000"/>
     <d v="2024-09-04T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1076"/>
@@ -9278,6 +10009,7 @@
     <n v="7500"/>
     <d v="2024-03-04T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1077"/>
@@ -9291,6 +10023,7 @@
     <n v="2500"/>
     <d v="2024-05-31T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1078"/>
@@ -9304,6 +10037,7 @@
     <n v="2500"/>
     <d v="2024-02-08T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1079"/>
@@ -9317,6 +10051,7 @@
     <n v="6000"/>
     <d v="2024-06-10T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1080"/>
@@ -9330,6 +10065,7 @@
     <n v="6000"/>
     <d v="2024-01-06T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1081"/>
@@ -9343,6 +10079,7 @@
     <n v="10000"/>
     <d v="2024-11-05T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1082"/>
@@ -9356,6 +10093,7 @@
     <n v="50000"/>
     <d v="2024-04-11T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1083"/>
@@ -9369,6 +10107,7 @@
     <n v="100000"/>
     <d v="2024-10-10T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1084"/>
@@ -9382,6 +10121,7 @@
     <n v="7500"/>
     <d v="2024-08-21T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1085"/>
@@ -9395,6 +10135,7 @@
     <n v="12500"/>
     <d v="2024-11-09T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1086"/>
@@ -9408,6 +10149,7 @@
     <n v="20000"/>
     <d v="2024-03-26T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1087"/>
@@ -9421,6 +10163,7 @@
     <n v="5000"/>
     <d v="2024-02-17T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1088"/>
@@ -9434,6 +10177,7 @@
     <n v="15000"/>
     <d v="2024-04-01T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1089"/>
@@ -9447,6 +10191,7 @@
     <n v="6000"/>
     <d v="2024-11-24T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1090"/>
@@ -9460,6 +10205,7 @@
     <n v="20000"/>
     <d v="2024-03-18T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1091"/>
@@ -9473,6 +10219,7 @@
     <n v="4000"/>
     <d v="2024-07-26T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1092"/>
@@ -9486,6 +10233,7 @@
     <n v="4500"/>
     <d v="2024-07-25T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1093"/>
@@ -9499,6 +10247,7 @@
     <n v="6000"/>
     <d v="2024-08-30T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1094"/>
@@ -9512,6 +10261,7 @@
     <n v="250000"/>
     <d v="2024-01-11T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1095"/>
@@ -9525,6 +10275,7 @@
     <n v="40000"/>
     <d v="2024-11-02T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1096"/>
@@ -9538,6 +10289,7 @@
     <n v="6000"/>
     <d v="2024-10-11T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1097"/>
@@ -9551,6 +10303,7 @@
     <n v="12000"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1098"/>
@@ -9564,6 +10317,7 @@
     <n v="80000"/>
     <d v="2024-02-07T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1099"/>
@@ -9577,6 +10331,7 @@
     <n v="250000"/>
     <d v="2024-02-18T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1100"/>
@@ -9590,6 +10345,7 @@
     <n v="5000"/>
     <d v="2024-12-07T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1101"/>
@@ -9603,6 +10359,7 @@
     <n v="4500"/>
     <d v="2024-03-27T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1102"/>
@@ -9616,6 +10373,7 @@
     <n v="50000"/>
     <d v="2024-03-06T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1103"/>
@@ -9629,6 +10387,7 @@
     <n v="40000"/>
     <d v="2024-07-23T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1104"/>
@@ -9642,6 +10401,7 @@
     <n v="100000"/>
     <d v="2024-09-20T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1105"/>
@@ -9655,6 +10415,7 @@
     <n v="10000"/>
     <d v="2024-04-08T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1106"/>
@@ -9668,6 +10429,7 @@
     <n v="25000"/>
     <d v="2024-07-22T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1107"/>
@@ -9681,6 +10443,7 @@
     <n v="2500"/>
     <d v="2024-08-01T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1108"/>
@@ -9694,6 +10457,7 @@
     <n v="2500"/>
     <d v="2024-08-08T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1109"/>
@@ -9707,6 +10471,7 @@
     <n v="4000"/>
     <d v="2024-12-02T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1110"/>
@@ -9720,6 +10485,7 @@
     <n v="6000"/>
     <d v="2024-02-25T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1111"/>
@@ -9733,6 +10499,7 @@
     <n v="1500"/>
     <d v="2024-07-02T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1112"/>
@@ -9746,6 +10513,7 @@
     <n v="7500"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1113"/>
@@ -9759,6 +10527,7 @@
     <n v="100000"/>
     <d v="2024-12-20T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1114"/>
@@ -9772,6 +10541,7 @@
     <n v="50000"/>
     <d v="2024-03-31T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1115"/>
@@ -9785,6 +10555,7 @@
     <n v="10000"/>
     <d v="2024-03-06T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1116"/>
@@ -9798,6 +10569,7 @@
     <n v="250000"/>
     <d v="2024-09-12T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1117"/>
@@ -9811,6 +10583,7 @@
     <n v="5000"/>
     <d v="2024-05-25T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1118"/>
@@ -9824,6 +10597,7 @@
     <n v="10000"/>
     <d v="2024-05-06T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1119"/>
@@ -9837,6 +10611,7 @@
     <n v="150000"/>
     <d v="2024-08-17T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1120"/>
@@ -9850,6 +10625,7 @@
     <n v="8000"/>
     <d v="2024-01-12T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1121"/>
@@ -9863,6 +10639,7 @@
     <n v="20000"/>
     <d v="2024-11-19T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1122"/>
@@ -9876,6 +10653,7 @@
     <n v="60000"/>
     <d v="2024-01-12T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1123"/>
@@ -9889,6 +10667,7 @@
     <n v="10000"/>
     <d v="2024-04-23T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1124"/>
@@ -9902,6 +10681,7 @@
     <n v="7500"/>
     <d v="2024-11-11T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1125"/>
@@ -9915,6 +10695,7 @@
     <n v="1600"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1126"/>
@@ -9928,6 +10709,7 @@
     <n v="60000"/>
     <d v="2024-05-13T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1127"/>
@@ -9941,6 +10723,7 @@
     <n v="5000"/>
     <d v="2024-02-04T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1128"/>
@@ -9954,6 +10737,7 @@
     <n v="25000"/>
     <d v="2024-11-01T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1129"/>
@@ -9967,6 +10751,7 @@
     <n v="3000"/>
     <d v="2024-03-17T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1130"/>
@@ -9980,6 +10765,7 @@
     <n v="1500"/>
     <d v="2024-07-04T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1131"/>
@@ -9993,6 +10779,7 @@
     <n v="6000"/>
     <d v="2024-12-04T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1132"/>
@@ -10006,6 +10793,7 @@
     <n v="4000"/>
     <d v="2024-05-09T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1133"/>
@@ -10019,6 +10807,7 @@
     <n v="8000"/>
     <d v="2024-03-09T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1134"/>
@@ -10032,6 +10821,7 @@
     <n v="100000"/>
     <d v="2024-01-26T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1135"/>
@@ -10045,6 +10835,7 @@
     <n v="6000"/>
     <d v="2024-01-19T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1136"/>
@@ -10058,6 +10849,7 @@
     <n v="9000"/>
     <d v="2024-04-14T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1137"/>
@@ -10071,6 +10863,7 @@
     <n v="10000"/>
     <d v="2024-12-07T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1138"/>
@@ -10084,6 +10877,7 @@
     <n v="10000"/>
     <d v="2024-09-27T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1139"/>
@@ -10097,6 +10891,7 @@
     <n v="5000"/>
     <d v="2024-09-15T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1140"/>
@@ -10110,6 +10905,7 @@
     <n v="20000"/>
     <d v="2024-10-17T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1141"/>
@@ -10123,6 +10919,7 @@
     <n v="3200"/>
     <d v="2024-01-22T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1142"/>
@@ -10136,6 +10933,7 @@
     <n v="5000"/>
     <d v="2024-12-22T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1143"/>
@@ -10149,6 +10947,7 @@
     <n v="4000"/>
     <d v="2024-02-13T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1144"/>
@@ -10162,6 +10961,7 @@
     <n v="80000"/>
     <d v="2024-08-02T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1145"/>
@@ -10175,6 +10975,7 @@
     <n v="150000"/>
     <d v="2024-05-27T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1146"/>
@@ -10188,6 +10989,7 @@
     <n v="10000"/>
     <d v="2024-04-27T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1147"/>
@@ -10201,6 +11003,7 @@
     <n v="800"/>
     <d v="2024-08-30T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1148"/>
@@ -10214,6 +11017,7 @@
     <n v="10000"/>
     <d v="2024-08-28T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1149"/>
@@ -10227,6 +11031,7 @@
     <n v="12000"/>
     <d v="2024-01-24T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1150"/>
@@ -10240,6 +11045,7 @@
     <n v="25000"/>
     <d v="2024-05-21T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1151"/>
@@ -10253,6 +11059,7 @@
     <n v="5000"/>
     <d v="2024-03-13T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1152"/>
@@ -10266,6 +11073,7 @@
     <n v="12000"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1153"/>
@@ -10279,6 +11087,7 @@
     <n v="100000"/>
     <d v="2024-10-23T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1154"/>
@@ -10292,6 +11101,7 @@
     <n v="150000"/>
     <d v="2024-04-26T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1155"/>
@@ -10305,6 +11115,7 @@
     <n v="1500"/>
     <d v="2024-02-25T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1156"/>
@@ -10318,6 +11129,7 @@
     <n v="20000"/>
     <d v="2024-08-26T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1157"/>
@@ -10331,6 +11143,7 @@
     <n v="1600"/>
     <d v="2024-08-24T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1158"/>
@@ -10344,6 +11157,7 @@
     <n v="800"/>
     <d v="2024-03-02T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1159"/>
@@ -10357,6 +11171,7 @@
     <n v="9000"/>
     <d v="2024-06-16T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1160"/>
@@ -10370,6 +11185,7 @@
     <n v="80000"/>
     <d v="2024-10-28T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1161"/>
@@ -10383,6 +11199,7 @@
     <n v="50000"/>
     <d v="2024-11-13T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1162"/>
@@ -10396,6 +11213,7 @@
     <n v="50000"/>
     <d v="2024-07-25T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1163"/>
@@ -10409,6 +11227,7 @@
     <n v="15000"/>
     <d v="2024-05-13T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1164"/>
@@ -10422,6 +11241,7 @@
     <n v="200000"/>
     <d v="2024-10-13T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1165"/>
@@ -10435,6 +11255,7 @@
     <n v="6000"/>
     <d v="2024-01-23T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1166"/>
@@ -10448,6 +11269,7 @@
     <n v="12000"/>
     <d v="2024-07-12T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1167"/>
@@ -10461,6 +11283,7 @@
     <n v="5000"/>
     <d v="2024-07-04T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1168"/>
@@ -10474,6 +11297,7 @@
     <n v="100000"/>
     <d v="2024-08-28T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1169"/>
@@ -10487,6 +11311,7 @@
     <n v="25000"/>
     <d v="2024-04-17T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1170"/>
@@ -10500,6 +11325,7 @@
     <n v="50000"/>
     <d v="2024-11-19T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1171"/>
@@ -10513,6 +11339,7 @@
     <n v="7500"/>
     <d v="2024-03-17T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1172"/>
@@ -10526,6 +11353,7 @@
     <n v="5000"/>
     <d v="2024-09-18T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1173"/>
@@ -10539,6 +11367,7 @@
     <n v="10000"/>
     <d v="2024-07-02T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1174"/>
@@ -10552,6 +11381,7 @@
     <n v="12000"/>
     <d v="2024-09-12T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1175"/>
@@ -10565,6 +11395,7 @@
     <n v="15000"/>
     <d v="2024-01-11T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1176"/>
@@ -10578,6 +11409,7 @@
     <n v="6000"/>
     <d v="2024-02-02T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1177"/>
@@ -10591,6 +11423,7 @@
     <n v="1600"/>
     <d v="2024-11-26T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1178"/>
@@ -10604,6 +11437,7 @@
     <n v="80000"/>
     <d v="2024-11-17T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1179"/>
@@ -10617,6 +11451,7 @@
     <n v="4000"/>
     <d v="2024-05-12T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1180"/>
@@ -10630,6 +11465,7 @@
     <n v="100000"/>
     <d v="2024-06-22T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1181"/>
@@ -10643,6 +11479,7 @@
     <n v="3200"/>
     <d v="2024-01-27T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1182"/>
@@ -10656,6 +11493,7 @@
     <n v="6000"/>
     <d v="2024-06-12T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1183"/>
@@ -10669,6 +11507,7 @@
     <n v="60000"/>
     <d v="2024-12-04T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1184"/>
@@ -10682,6 +11521,7 @@
     <n v="100000"/>
     <d v="2024-07-22T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1185"/>
@@ -10695,6 +11535,7 @@
     <n v="7500"/>
     <d v="2024-09-16T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1186"/>
@@ -10708,6 +11549,7 @@
     <n v="5000"/>
     <d v="2024-04-12T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1187"/>
@@ -10721,6 +11563,7 @@
     <n v="15000"/>
     <d v="2024-06-19T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1188"/>
@@ -10734,6 +11577,7 @@
     <n v="4000"/>
     <d v="2024-05-23T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1189"/>
@@ -10747,6 +11591,7 @@
     <n v="15000"/>
     <d v="2024-09-11T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1190"/>
@@ -10760,6 +11605,7 @@
     <n v="15000"/>
     <d v="2024-05-04T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1191"/>
@@ -10773,6 +11619,7 @@
     <n v="20000"/>
     <d v="2024-08-01T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1192"/>
@@ -10786,6 +11633,7 @@
     <n v="10000"/>
     <d v="2024-05-17T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1193"/>
@@ -10799,6 +11647,7 @@
     <n v="200000"/>
     <d v="2024-06-27T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1194"/>
@@ -10812,6 +11661,7 @@
     <n v="3200"/>
     <d v="2024-02-06T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1195"/>
@@ -10825,6 +11675,7 @@
     <n v="3000"/>
     <d v="2024-07-22T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1196"/>
@@ -10838,6 +11689,7 @@
     <n v="6000"/>
     <d v="2024-01-11T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1197"/>
@@ -10851,6 +11703,7 @@
     <n v="10000"/>
     <d v="2024-07-13T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1198"/>
@@ -10864,6 +11717,7 @@
     <n v="12500"/>
     <d v="2024-02-22T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1199"/>
@@ -10877,6 +11731,7 @@
     <n v="20000"/>
     <d v="2024-11-05T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1200"/>
@@ -10890,6 +11745,7 @@
     <n v="15000"/>
     <d v="2024-05-04T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1201"/>
@@ -10903,6 +11759,7 @@
     <n v="150000"/>
     <d v="2024-10-26T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1202"/>
@@ -10916,6 +11773,7 @@
     <n v="12500"/>
     <d v="2024-01-09T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1203"/>
@@ -10929,6 +11787,7 @@
     <n v="80000"/>
     <d v="2024-11-12T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1204"/>
@@ -10942,6 +11801,7 @@
     <n v="7500"/>
     <d v="2024-03-30T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1205"/>
@@ -10955,6 +11815,7 @@
     <n v="5000"/>
     <d v="2024-08-10T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1206"/>
@@ -10968,6 +11829,7 @@
     <n v="250000"/>
     <d v="2024-03-20T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1207"/>
@@ -10981,6 +11843,7 @@
     <n v="40000"/>
     <d v="2024-03-20T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1208"/>
@@ -10994,6 +11857,7 @@
     <n v="20000"/>
     <d v="2024-11-10T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1209"/>
@@ -11007,6 +11871,7 @@
     <n v="6000"/>
     <d v="2024-11-20T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1210"/>
@@ -11020,6 +11885,7 @@
     <n v="5000"/>
     <d v="2024-05-24T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1211"/>
@@ -11033,6 +11899,7 @@
     <n v="80000"/>
     <d v="2024-05-22T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1212"/>
@@ -11046,6 +11913,7 @@
     <n v="2500"/>
     <d v="2024-06-23T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1213"/>
@@ -11059,6 +11927,7 @@
     <n v="8000"/>
     <d v="2024-07-19T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1214"/>
@@ -11072,6 +11941,7 @@
     <n v="10000"/>
     <d v="2024-08-11T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1215"/>
@@ -11085,6 +11955,7 @@
     <n v="3000"/>
     <d v="2024-08-09T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1216"/>
@@ -11098,6 +11969,7 @@
     <n v="15000"/>
     <d v="2024-03-04T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1217"/>
@@ -11111,6 +11983,7 @@
     <n v="2400"/>
     <d v="2024-12-27T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1218"/>
@@ -11124,6 +11997,7 @@
     <n v="8000"/>
     <d v="2024-05-24T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1219"/>
@@ -11137,6 +12011,7 @@
     <n v="12000"/>
     <d v="2024-12-13T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1220"/>
@@ -11150,6 +12025,7 @@
     <n v="4500"/>
     <d v="2024-02-09T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1221"/>
@@ -11163,6 +12039,7 @@
     <n v="9000"/>
     <d v="2024-08-14T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1222"/>
@@ -11176,6 +12053,7 @@
     <n v="5000"/>
     <d v="2024-01-08T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1223"/>
@@ -11189,6 +12067,7 @@
     <n v="3200"/>
     <d v="2024-12-13T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1224"/>
@@ -11202,6 +12081,7 @@
     <n v="80000"/>
     <d v="2024-06-25T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1225"/>
@@ -11215,6 +12095,7 @@
     <n v="10000"/>
     <d v="2024-02-25T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1226"/>
@@ -11228,6 +12109,7 @@
     <n v="80000"/>
     <d v="2024-08-21T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1227"/>
@@ -11241,6 +12123,7 @@
     <n v="9000"/>
     <d v="2024-03-31T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1228"/>
@@ -11254,6 +12137,7 @@
     <n v="2400"/>
     <d v="2024-12-26T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1229"/>
@@ -11267,6 +12151,7 @@
     <n v="4000"/>
     <d v="2024-08-26T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1230"/>
@@ -11280,6 +12165,7 @@
     <n v="7500"/>
     <d v="2024-12-16T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1231"/>
@@ -11293,6 +12179,7 @@
     <n v="50000"/>
     <d v="2024-07-25T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1232"/>
@@ -11306,6 +12193,7 @@
     <n v="80000"/>
     <d v="2024-09-24T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1233"/>
@@ -11319,6 +12207,7 @@
     <n v="4500"/>
     <d v="2024-07-07T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1234"/>
@@ -11332,6 +12221,7 @@
     <n v="5000"/>
     <d v="2024-07-04T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1235"/>
@@ -11345,6 +12235,7 @@
     <n v="5000"/>
     <d v="2024-04-22T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1236"/>
@@ -11358,6 +12249,7 @@
     <n v="10000"/>
     <d v="2024-09-16T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1237"/>
@@ -11371,6 +12263,7 @@
     <n v="10000"/>
     <d v="2024-11-18T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1238"/>
@@ -11384,6 +12277,7 @@
     <n v="100000"/>
     <d v="2024-06-22T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1239"/>
@@ -11397,6 +12291,7 @@
     <n v="2000"/>
     <d v="2024-02-26T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1240"/>
@@ -11410,6 +12305,7 @@
     <n v="20000"/>
     <d v="2024-03-17T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1241"/>
@@ -11423,6 +12319,7 @@
     <n v="6000"/>
     <d v="2024-05-12T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1242"/>
@@ -11436,6 +12333,7 @@
     <n v="100000"/>
     <d v="2024-06-12T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1243"/>
@@ -11449,6 +12347,7 @@
     <n v="10000"/>
     <d v="2024-04-30T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1244"/>
@@ -11462,6 +12361,7 @@
     <n v="800"/>
     <d v="2024-04-07T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1245"/>
@@ -11475,6 +12375,7 @@
     <n v="100000"/>
     <d v="2024-06-28T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1246"/>
@@ -11488,6 +12389,7 @@
     <n v="20000"/>
     <d v="2024-07-08T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1247"/>
@@ -11501,6 +12403,7 @@
     <n v="2400"/>
     <d v="2024-01-03T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1248"/>
@@ -11514,6 +12417,7 @@
     <n v="150000"/>
     <d v="2024-12-24T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1249"/>
@@ -11527,6 +12431,7 @@
     <n v="200000"/>
     <d v="2024-06-04T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1250"/>
@@ -11540,6 +12445,7 @@
     <n v="20000"/>
     <d v="2024-06-13T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1251"/>
@@ -11553,6 +12459,7 @@
     <n v="7500"/>
     <d v="2024-04-15T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1252"/>
@@ -11566,6 +12473,7 @@
     <n v="20000"/>
     <d v="2024-03-22T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1253"/>
@@ -11579,6 +12487,7 @@
     <n v="8000"/>
     <d v="2024-12-29T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1254"/>
@@ -11592,6 +12501,7 @@
     <n v="20000"/>
     <d v="2024-11-29T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1255"/>
@@ -11605,6 +12515,7 @@
     <n v="150000"/>
     <d v="2024-06-16T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1256"/>
@@ -11618,6 +12529,7 @@
     <n v="150000"/>
     <d v="2024-05-18T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1257"/>
@@ -11631,6 +12543,7 @@
     <n v="3000"/>
     <d v="2024-02-18T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1258"/>
@@ -11644,6 +12557,7 @@
     <n v="6000"/>
     <d v="2024-09-21T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1259"/>
@@ -11657,6 +12571,7 @@
     <n v="5000"/>
     <d v="2024-01-04T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1260"/>
@@ -11670,6 +12585,7 @@
     <n v="250000"/>
     <d v="2024-07-12T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1261"/>
@@ -11683,6 +12599,7 @@
     <n v="5000"/>
     <d v="2024-01-16T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1262"/>
@@ -11696,6 +12613,7 @@
     <n v="200000"/>
     <d v="2024-12-12T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1263"/>
@@ -11709,6 +12627,7 @@
     <n v="80000"/>
     <d v="2024-05-06T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1264"/>
@@ -11722,6 +12641,7 @@
     <n v="6000"/>
     <d v="2024-11-09T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1265"/>
@@ -11735,6 +12655,7 @@
     <n v="10000"/>
     <d v="2024-06-19T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1266"/>
@@ -11748,6 +12669,7 @@
     <n v="20000"/>
     <d v="2024-10-05T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1267"/>
@@ -11761,6 +12683,7 @@
     <n v="6000"/>
     <d v="2024-01-23T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1268"/>
@@ -11774,6 +12697,7 @@
     <n v="12500"/>
     <d v="2024-10-14T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1269"/>
@@ -11787,6 +12711,7 @@
     <n v="4500"/>
     <d v="2024-06-14T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1270"/>
@@ -11800,6 +12725,7 @@
     <n v="1600"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1271"/>
@@ -11813,6 +12739,7 @@
     <n v="6000"/>
     <d v="2024-03-21T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1272"/>
@@ -11826,6 +12753,7 @@
     <n v="200000"/>
     <d v="2024-07-28T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1273"/>
@@ -11839,6 +12767,7 @@
     <n v="6000"/>
     <d v="2024-04-07T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1274"/>
@@ -11852,6 +12781,7 @@
     <n v="6000"/>
     <d v="2024-01-24T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1275"/>
@@ -11865,6 +12795,7 @@
     <n v="6000"/>
     <d v="2024-12-08T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1276"/>
@@ -11878,6 +12809,7 @@
     <n v="80000"/>
     <d v="2024-10-31T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1277"/>
@@ -11891,6 +12823,7 @@
     <n v="2000"/>
     <d v="2024-11-28T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1278"/>
@@ -11904,6 +12837,7 @@
     <n v="15000"/>
     <d v="2024-11-04T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1279"/>
@@ -11917,6 +12851,7 @@
     <n v="6000"/>
     <d v="2024-06-07T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1280"/>
@@ -11930,6 +12865,7 @@
     <n v="2000"/>
     <d v="2024-02-29T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1281"/>
@@ -11943,6 +12879,7 @@
     <n v="20000"/>
     <d v="2024-05-29T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1282"/>
@@ -11956,6 +12893,7 @@
     <n v="2400"/>
     <d v="2024-10-07T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1283"/>
@@ -11969,6 +12907,7 @@
     <n v="800"/>
     <d v="2024-08-01T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1284"/>
@@ -11982,6 +12921,7 @@
     <n v="2500"/>
     <d v="2024-03-10T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1285"/>
@@ -11995,6 +12935,7 @@
     <n v="15000"/>
     <d v="2024-09-06T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1286"/>
@@ -12008,6 +12949,7 @@
     <n v="7500"/>
     <d v="2024-12-04T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1287"/>
@@ -12021,6 +12963,7 @@
     <n v="20000"/>
     <d v="2024-01-30T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1288"/>
@@ -12034,6 +12977,7 @@
     <n v="100000"/>
     <d v="2024-02-11T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1289"/>
@@ -12047,6 +12991,7 @@
     <n v="100000"/>
     <d v="2024-01-20T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1290"/>
@@ -12060,6 +13005,7 @@
     <n v="150000"/>
     <d v="2024-05-22T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1291"/>
@@ -12073,6 +13019,7 @@
     <n v="6000"/>
     <d v="2024-10-03T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1292"/>
@@ -12086,6 +13033,7 @@
     <n v="15000"/>
     <d v="2024-02-24T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1293"/>
@@ -12099,6 +13047,7 @@
     <n v="20000"/>
     <d v="2024-04-16T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1294"/>
@@ -12112,6 +13061,7 @@
     <n v="12500"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1295"/>
@@ -12125,6 +13075,7 @@
     <n v="6000"/>
     <d v="2024-11-23T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1296"/>
@@ -12138,6 +13089,7 @@
     <n v="100000"/>
     <d v="2024-03-15T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1297"/>
@@ -12151,6 +13103,7 @@
     <n v="2400"/>
     <d v="2024-10-25T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1298"/>
@@ -12164,6 +13117,7 @@
     <n v="3000"/>
     <d v="2024-10-17T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1299"/>
@@ -12177,6 +13131,7 @@
     <n v="6000"/>
     <d v="2024-09-18T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1300"/>
@@ -12190,6 +13145,7 @@
     <n v="3000"/>
     <d v="2024-08-27T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1301"/>
@@ -12203,6 +13159,7 @@
     <n v="3000"/>
     <d v="2024-06-12T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1302"/>
@@ -12216,6 +13173,7 @@
     <n v="1500"/>
     <d v="2024-06-04T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1303"/>
@@ -12229,6 +13187,7 @@
     <n v="8000"/>
     <d v="2024-07-30T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1304"/>
@@ -12242,6 +13201,7 @@
     <n v="200000"/>
     <d v="2024-08-05T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1305"/>
@@ -12255,6 +13215,7 @@
     <n v="12000"/>
     <d v="2024-02-22T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1306"/>
@@ -12268,6 +13229,7 @@
     <n v="6000"/>
     <d v="2024-04-08T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1307"/>
@@ -12281,6 +13243,7 @@
     <n v="3200"/>
     <d v="2024-09-05T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1308"/>
@@ -12294,6 +13257,7 @@
     <n v="12500"/>
     <d v="2024-02-07T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1309"/>
@@ -12307,6 +13271,7 @@
     <n v="2000"/>
     <d v="2024-06-14T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1310"/>
@@ -12320,6 +13285,7 @@
     <n v="3200"/>
     <d v="2024-07-10T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1311"/>
@@ -12333,6 +13299,7 @@
     <n v="1500"/>
     <d v="2024-11-23T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1312"/>
@@ -12346,6 +13313,7 @@
     <n v="12000"/>
     <d v="2024-02-05T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1313"/>
@@ -12359,6 +13327,7 @@
     <n v="150000"/>
     <d v="2024-04-07T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1314"/>
@@ -12372,6 +13341,7 @@
     <n v="2500"/>
     <d v="2024-10-27T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1315"/>
@@ -12385,6 +13355,7 @@
     <n v="4500"/>
     <d v="2024-06-21T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1316"/>
@@ -12398,6 +13369,7 @@
     <n v="80000"/>
     <d v="2024-11-17T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1317"/>
@@ -12411,6 +13383,7 @@
     <n v="50000"/>
     <d v="2024-04-06T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1318"/>
@@ -12424,6 +13397,7 @@
     <n v="25000"/>
     <d v="2024-11-07T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1319"/>
@@ -12437,6 +13411,7 @@
     <n v="12500"/>
     <d v="2024-05-15T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1320"/>
@@ -12450,6 +13425,7 @@
     <n v="12000"/>
     <d v="2024-11-09T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1321"/>
@@ -12463,6 +13439,7 @@
     <n v="50000"/>
     <d v="2024-06-17T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1322"/>
@@ -12476,6 +13453,7 @@
     <n v="3000"/>
     <d v="2024-09-18T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1323"/>
@@ -12489,6 +13467,7 @@
     <n v="2000"/>
     <d v="2024-07-17T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1324"/>
@@ -12502,6 +13481,7 @@
     <n v="20000"/>
     <d v="2024-08-17T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1325"/>
@@ -12515,6 +13495,7 @@
     <n v="4500"/>
     <d v="2024-03-10T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1326"/>
@@ -12528,6 +13509,7 @@
     <n v="2500"/>
     <d v="2024-04-02T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1327"/>
@@ -12541,6 +13523,7 @@
     <n v="50000"/>
     <d v="2024-03-14T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1328"/>
@@ -12554,6 +13537,7 @@
     <n v="1600"/>
     <d v="2024-08-13T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1329"/>
@@ -12567,6 +13551,7 @@
     <n v="15000"/>
     <d v="2024-07-29T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1330"/>
@@ -12580,6 +13565,7 @@
     <n v="250000"/>
     <d v="2024-12-12T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1331"/>
@@ -12593,6 +13579,7 @@
     <n v="2500"/>
     <d v="2024-10-25T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1332"/>
@@ -12606,6 +13593,7 @@
     <n v="10000"/>
     <d v="2024-04-16T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1333"/>
@@ -12619,6 +13607,7 @@
     <n v="250000"/>
     <d v="2024-05-08T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1334"/>
@@ -12632,6 +13621,7 @@
     <n v="15000"/>
     <d v="2024-06-13T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1335"/>
@@ -12645,6 +13635,7 @@
     <n v="4500"/>
     <d v="2024-04-13T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1336"/>
@@ -12658,6 +13649,7 @@
     <n v="15000"/>
     <d v="2024-06-30T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1337"/>
@@ -12671,6 +13663,7 @@
     <n v="6000"/>
     <d v="2024-04-21T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1338"/>
@@ -12684,6 +13677,7 @@
     <n v="200000"/>
     <d v="2024-02-04T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1339"/>
@@ -12697,6 +13691,7 @@
     <n v="5000"/>
     <d v="2024-03-10T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1340"/>
@@ -12710,6 +13705,7 @@
     <n v="3200"/>
     <d v="2024-07-21T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1341"/>
@@ -12723,6 +13719,7 @@
     <n v="10000"/>
     <d v="2024-06-11T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1342"/>
@@ -12736,6 +13733,7 @@
     <n v="12000"/>
     <d v="2024-02-24T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1343"/>
@@ -12749,6 +13747,7 @@
     <n v="6000"/>
     <d v="2024-03-27T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1344"/>
@@ -12762,6 +13761,7 @@
     <n v="200000"/>
     <d v="2024-06-09T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1345"/>
@@ -12775,6 +13775,7 @@
     <n v="6000"/>
     <d v="2024-03-14T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1346"/>
@@ -12788,6 +13789,7 @@
     <n v="80000"/>
     <d v="2024-06-26T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1347"/>
@@ -12801,6 +13803,7 @@
     <n v="15000"/>
     <d v="2024-01-19T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1348"/>
@@ -12814,6 +13817,7 @@
     <n v="40000"/>
     <d v="2024-01-10T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1349"/>
@@ -12827,6 +13831,7 @@
     <n v="2400"/>
     <d v="2024-11-03T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1350"/>
@@ -12840,6 +13845,7 @@
     <n v="5000"/>
     <d v="2024-01-24T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1351"/>
@@ -12853,6 +13859,7 @@
     <n v="1500"/>
     <d v="2024-01-04T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1352"/>
@@ -12866,6 +13873,7 @@
     <n v="6000"/>
     <d v="2024-10-27T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1353"/>
@@ -12879,6 +13887,7 @@
     <n v="80000"/>
     <d v="2024-10-27T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1354"/>
@@ -12892,6 +13901,7 @@
     <n v="2500"/>
     <d v="2024-04-05T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1355"/>
@@ -12905,6 +13915,7 @@
     <n v="12000"/>
     <d v="2024-10-02T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1356"/>
@@ -12918,6 +13929,7 @@
     <n v="9000"/>
     <d v="2024-07-31T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1357"/>
@@ -12931,6 +13943,7 @@
     <n v="12500"/>
     <d v="2024-11-25T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1358"/>
@@ -12944,6 +13957,7 @@
     <n v="1500"/>
     <d v="2024-11-10T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1359"/>
@@ -12957,6 +13971,7 @@
     <n v="2000"/>
     <d v="2024-02-25T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1360"/>
@@ -12970,6 +13985,7 @@
     <n v="8000"/>
     <d v="2024-12-30T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1361"/>
@@ -12983,6 +13999,7 @@
     <n v="2000"/>
     <d v="2024-02-21T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1362"/>
@@ -12996,6 +14013,7 @@
     <n v="2500"/>
     <d v="2024-12-05T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1363"/>
@@ -13009,6 +14027,7 @@
     <n v="1500"/>
     <d v="2024-05-11T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1364"/>
@@ -13022,6 +14041,7 @@
     <n v="4000"/>
     <d v="2024-05-28T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1365"/>
@@ -13035,6 +14055,7 @@
     <n v="1500"/>
     <d v="2024-01-23T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1366"/>
@@ -13048,6 +14069,7 @@
     <n v="6000"/>
     <d v="2024-04-10T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1367"/>
@@ -13061,6 +14083,7 @@
     <n v="4000"/>
     <d v="2024-05-29T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1368"/>
@@ -13074,6 +14097,7 @@
     <n v="800"/>
     <d v="2024-02-04T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1369"/>
@@ -13087,6 +14111,7 @@
     <n v="800"/>
     <d v="2024-05-18T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1370"/>
@@ -13100,6 +14125,7 @@
     <n v="4000"/>
     <d v="2024-09-01T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1371"/>
@@ -13113,6 +14139,7 @@
     <n v="7500"/>
     <d v="2024-12-13T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1372"/>
@@ -13126,6 +14153,7 @@
     <n v="15000"/>
     <d v="2024-05-07T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1373"/>
@@ -13139,6 +14167,7 @@
     <n v="5000"/>
     <d v="2024-12-04T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1374"/>
@@ -13152,6 +14181,7 @@
     <n v="12000"/>
     <d v="2024-10-24T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1375"/>
@@ -13165,6 +14195,7 @@
     <n v="12000"/>
     <d v="2024-05-24T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1376"/>
@@ -13178,6 +14209,7 @@
     <n v="20000"/>
     <d v="2024-08-05T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1377"/>
@@ -13191,6 +14223,7 @@
     <n v="1600"/>
     <d v="2024-10-08T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1378"/>
@@ -13204,6 +14237,7 @@
     <n v="100000"/>
     <d v="2024-10-04T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1379"/>
@@ -13217,6 +14251,7 @@
     <n v="12000"/>
     <d v="2024-12-05T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1380"/>
@@ -13230,6 +14265,7 @@
     <n v="2400"/>
     <d v="2024-09-14T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1381"/>
@@ -13243,6 +14279,7 @@
     <n v="20000"/>
     <d v="2024-01-07T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1382"/>
@@ -13256,6 +14293,7 @@
     <n v="50000"/>
     <d v="2024-08-04T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1383"/>
@@ -13269,6 +14307,7 @@
     <n v="1500"/>
     <d v="2024-09-17T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1384"/>
@@ -13282,6 +14321,7 @@
     <n v="4500"/>
     <d v="2024-10-26T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1385"/>
@@ -13295,6 +14335,7 @@
     <n v="5000"/>
     <d v="2024-09-26T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1386"/>
@@ -13308,6 +14349,7 @@
     <n v="1500"/>
     <d v="2024-09-26T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1387"/>
@@ -13321,6 +14363,7 @@
     <n v="6000"/>
     <d v="2024-01-23T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1388"/>
@@ -13334,6 +14377,7 @@
     <n v="6000"/>
     <d v="2024-11-13T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1389"/>
@@ -13347,6 +14391,7 @@
     <n v="60000"/>
     <d v="2024-12-16T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1390"/>
@@ -13360,6 +14405,7 @@
     <n v="5000"/>
     <d v="2024-07-06T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1391"/>
@@ -13373,6 +14419,7 @@
     <n v="100000"/>
     <d v="2024-06-21T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1392"/>
@@ -13386,6 +14433,7 @@
     <n v="3000"/>
     <d v="2024-07-27T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1393"/>
@@ -13399,6 +14447,7 @@
     <n v="2500"/>
     <d v="2024-09-02T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1394"/>
@@ -13412,6 +14461,7 @@
     <n v="10000"/>
     <d v="2024-12-29T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1395"/>
@@ -13425,6 +14475,7 @@
     <n v="200000"/>
     <d v="2024-09-11T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1396"/>
@@ -13438,6 +14489,7 @@
     <n v="10000"/>
     <d v="2024-08-16T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1397"/>
@@ -13451,6 +14503,7 @@
     <n v="3200"/>
     <d v="2024-11-05T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1398"/>
@@ -13464,6 +14517,7 @@
     <n v="20000"/>
     <d v="2024-08-04T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1399"/>
@@ -13477,6 +14531,7 @@
     <n v="10000"/>
     <d v="2024-09-21T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1400"/>
@@ -13490,6 +14545,7 @@
     <n v="2000"/>
     <d v="2024-06-20T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1401"/>
@@ -13503,6 +14559,7 @@
     <n v="3200"/>
     <d v="2024-01-04T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1402"/>
@@ -13516,6 +14573,7 @@
     <n v="200000"/>
     <d v="2024-11-14T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1403"/>
@@ -13529,6 +14587,7 @@
     <n v="15000"/>
     <d v="2024-05-09T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1404"/>
@@ -13542,6 +14601,7 @@
     <n v="3000"/>
     <d v="2024-11-09T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1405"/>
@@ -13555,6 +14615,7 @@
     <n v="100000"/>
     <d v="2024-05-17T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1406"/>
@@ -13568,6 +14629,7 @@
     <n v="2500"/>
     <d v="2024-09-30T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1407"/>
@@ -13581,6 +14643,7 @@
     <n v="9000"/>
     <d v="2024-08-09T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1408"/>
@@ -13594,6 +14657,7 @@
     <n v="2400"/>
     <d v="2024-05-22T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1409"/>
@@ -13607,6 +14671,7 @@
     <n v="6000"/>
     <d v="2024-12-26T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1410"/>
@@ -13620,6 +14685,7 @@
     <n v="10000"/>
     <d v="2024-10-18T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1411"/>
@@ -13633,6 +14699,7 @@
     <n v="100000"/>
     <d v="2024-10-30T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1412"/>
@@ -13646,6 +14713,7 @@
     <n v="4000"/>
     <d v="2024-12-14T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1413"/>
@@ -13659,6 +14727,7 @@
     <n v="20000"/>
     <d v="2024-09-04T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1414"/>
@@ -13672,6 +14741,7 @@
     <n v="7500"/>
     <d v="2024-01-22T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1415"/>
@@ -13685,6 +14755,7 @@
     <n v="6000"/>
     <d v="2024-11-23T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1416"/>
@@ -13698,6 +14769,7 @@
     <n v="20000"/>
     <d v="2024-08-20T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1417"/>
@@ -13711,6 +14783,7 @@
     <n v="5000"/>
     <d v="2024-09-12T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1418"/>
@@ -13724,6 +14797,7 @@
     <n v="10000"/>
     <d v="2024-07-19T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1419"/>
@@ -13737,6 +14811,7 @@
     <n v="40000"/>
     <d v="2024-02-24T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1420"/>
@@ -13750,6 +14825,7 @@
     <n v="60000"/>
     <d v="2024-05-20T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1421"/>
@@ -13763,6 +14839,7 @@
     <n v="800"/>
     <d v="2024-08-21T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1422"/>
@@ -13776,6 +14853,7 @@
     <n v="2400"/>
     <d v="2024-06-29T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1423"/>
@@ -13789,6 +14867,7 @@
     <n v="1600"/>
     <d v="2024-07-26T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1424"/>
@@ -13802,6 +14881,7 @@
     <n v="3200"/>
     <d v="2024-11-09T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1425"/>
@@ -13815,6 +14895,7 @@
     <n v="100000"/>
     <d v="2024-03-17T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1426"/>
@@ -13828,6 +14909,7 @@
     <n v="6000"/>
     <d v="2024-05-19T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1427"/>
@@ -13841,6 +14923,7 @@
     <n v="3000"/>
     <d v="2024-06-22T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1428"/>
@@ -13854,6 +14937,7 @@
     <n v="2000"/>
     <d v="2024-02-17T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1429"/>
@@ -13867,6 +14951,7 @@
     <n v="3200"/>
     <d v="2024-03-22T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1430"/>
@@ -13880,6 +14965,7 @@
     <n v="10000"/>
     <d v="2024-03-01T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1431"/>
@@ -13893,6 +14979,7 @@
     <n v="1500"/>
     <d v="2024-10-31T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1432"/>
@@ -13906,6 +14993,7 @@
     <n v="200000"/>
     <d v="2024-06-12T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1433"/>
@@ -13919,6 +15007,7 @@
     <n v="50000"/>
     <d v="2024-08-20T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1434"/>
@@ -13932,6 +15021,7 @@
     <n v="5000"/>
     <d v="2024-01-17T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1435"/>
@@ -13945,6 +15035,7 @@
     <n v="9000"/>
     <d v="2024-05-19T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1436"/>
@@ -13958,6 +15049,7 @@
     <n v="1600"/>
     <d v="2024-06-27T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1437"/>
@@ -13971,6 +15063,7 @@
     <n v="8000"/>
     <d v="2024-08-14T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1438"/>
@@ -13984,6 +15077,7 @@
     <n v="100000"/>
     <d v="2024-01-14T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1439"/>
@@ -13997,6 +15091,7 @@
     <n v="2400"/>
     <d v="2024-04-16T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1440"/>
@@ -14010,6 +15105,7 @@
     <n v="3000"/>
     <d v="2024-01-20T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1441"/>
@@ -14023,6 +15119,7 @@
     <n v="6000"/>
     <d v="2024-07-15T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1442"/>
@@ -14036,6 +15133,7 @@
     <n v="4500"/>
     <d v="2024-06-03T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1443"/>
@@ -14049,6 +15147,7 @@
     <n v="150000"/>
     <d v="2024-01-23T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1444"/>
@@ -14062,6 +15161,7 @@
     <n v="1500"/>
     <d v="2024-07-05T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1445"/>
@@ -14075,6 +15175,7 @@
     <n v="1500"/>
     <d v="2024-04-08T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1446"/>
@@ -14088,6 +15189,7 @@
     <n v="4000"/>
     <d v="2024-10-12T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1447"/>
@@ -14101,6 +15203,7 @@
     <n v="4500"/>
     <d v="2024-03-21T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1448"/>
@@ -14114,6 +15217,7 @@
     <n v="40000"/>
     <d v="2024-01-05T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1449"/>
@@ -14127,6 +15231,7 @@
     <n v="4500"/>
     <d v="2024-10-19T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1450"/>
@@ -14140,6 +15245,7 @@
     <n v="3000"/>
     <d v="2024-12-15T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1451"/>
@@ -14153,6 +15259,7 @@
     <n v="250000"/>
     <d v="2024-12-21T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1452"/>
@@ -14166,6 +15273,7 @@
     <n v="1600"/>
     <d v="2024-10-14T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1453"/>
@@ -14179,6 +15287,7 @@
     <n v="6000"/>
     <d v="2024-02-24T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1454"/>
@@ -14192,6 +15301,7 @@
     <n v="10000"/>
     <d v="2024-02-16T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1455"/>
@@ -14205,6 +15315,7 @@
     <n v="1600"/>
     <d v="2024-09-07T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1456"/>
@@ -14218,6 +15329,7 @@
     <n v="2500"/>
     <d v="2024-06-12T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1457"/>
@@ -14231,6 +15343,7 @@
     <n v="5000"/>
     <d v="2024-07-17T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1458"/>
@@ -14244,6 +15357,7 @@
     <n v="800"/>
     <d v="2024-07-28T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1459"/>
@@ -14257,6 +15371,7 @@
     <n v="1500"/>
     <d v="2024-12-27T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1460"/>
@@ -14270,6 +15385,7 @@
     <n v="10000"/>
     <d v="2024-04-02T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1461"/>
@@ -14283,6 +15399,7 @@
     <n v="1600"/>
     <d v="2024-05-13T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1462"/>
@@ -14296,6 +15413,7 @@
     <n v="100000"/>
     <d v="2024-09-10T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1463"/>
@@ -14309,6 +15427,7 @@
     <n v="100000"/>
     <d v="2024-08-11T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1464"/>
@@ -14322,6 +15441,7 @@
     <n v="4000"/>
     <d v="2024-03-29T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1465"/>
@@ -14335,6 +15455,7 @@
     <n v="12500"/>
     <d v="2024-06-08T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1466"/>
@@ -14348,6 +15469,7 @@
     <n v="40000"/>
     <d v="2024-06-08T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1467"/>
@@ -14361,6 +15483,7 @@
     <n v="6000"/>
     <d v="2024-12-21T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1468"/>
@@ -14374,6 +15497,7 @@
     <n v="40000"/>
     <d v="2024-01-01T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1469"/>
@@ -14387,6 +15511,7 @@
     <n v="150000"/>
     <d v="2024-10-27T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1470"/>
@@ -14400,6 +15525,7 @@
     <n v="3200"/>
     <d v="2024-02-07T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1471"/>
@@ -14413,6 +15539,7 @@
     <n v="5000"/>
     <d v="2024-11-20T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1472"/>
@@ -14426,6 +15553,7 @@
     <n v="800"/>
     <d v="2024-07-09T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1473"/>
@@ -14439,6 +15567,7 @@
     <n v="2500"/>
     <d v="2024-07-04T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1474"/>
@@ -14452,6 +15581,7 @@
     <n v="8000"/>
     <d v="2024-11-21T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1475"/>
@@ -14465,6 +15595,7 @@
     <n v="80000"/>
     <d v="2024-01-15T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1476"/>
@@ -14478,6 +15609,7 @@
     <n v="6000"/>
     <d v="2024-08-19T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1477"/>
@@ -14491,6 +15623,7 @@
     <n v="2500"/>
     <d v="2024-11-04T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1478"/>
@@ -14504,6 +15637,7 @@
     <n v="200000"/>
     <d v="2024-06-07T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1479"/>
@@ -14517,6 +15651,7 @@
     <n v="100000"/>
     <d v="2024-01-28T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1480"/>
@@ -14530,6 +15665,7 @@
     <n v="12000"/>
     <d v="2024-06-24T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1481"/>
@@ -14543,6 +15679,7 @@
     <n v="6000"/>
     <d v="2024-12-12T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1482"/>
@@ -14556,6 +15693,7 @@
     <n v="800"/>
     <d v="2024-03-14T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1483"/>
@@ -14569,6 +15707,7 @@
     <n v="80000"/>
     <d v="2024-03-14T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1484"/>
@@ -14582,6 +15721,7 @@
     <n v="40000"/>
     <d v="2024-06-01T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1485"/>
@@ -14595,6 +15735,7 @@
     <n v="12500"/>
     <d v="2024-08-30T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1486"/>
@@ -14608,6 +15749,7 @@
     <n v="2000"/>
     <d v="2024-06-20T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1487"/>
@@ -14621,6 +15763,7 @@
     <n v="8000"/>
     <d v="2024-05-05T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1488"/>
@@ -14634,6 +15777,7 @@
     <n v="3000"/>
     <d v="2024-04-08T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1489"/>
@@ -14647,6 +15791,7 @@
     <n v="40000"/>
     <d v="2024-10-08T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1490"/>
@@ -14660,6 +15805,7 @@
     <n v="100000"/>
     <d v="2024-05-02T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1491"/>
@@ -14673,6 +15819,7 @@
     <n v="12500"/>
     <d v="2024-06-14T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1492"/>
@@ -14686,6 +15833,7 @@
     <n v="800"/>
     <d v="2024-04-10T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1493"/>
@@ -14699,6 +15847,7 @@
     <n v="12000"/>
     <d v="2024-11-22T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1494"/>
@@ -14712,6 +15861,7 @@
     <n v="80000"/>
     <d v="2024-01-08T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1495"/>
@@ -14725,6 +15875,7 @@
     <n v="6000"/>
     <d v="2024-06-28T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1496"/>
@@ -14738,6 +15889,7 @@
     <n v="60000"/>
     <d v="2024-08-12T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1497"/>
@@ -14751,6 +15903,7 @@
     <n v="4000"/>
     <d v="2024-11-02T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1498"/>
@@ -14764,6 +15917,7 @@
     <n v="1500"/>
     <d v="2024-10-16T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1499"/>
@@ -14777,6 +15931,7 @@
     <n v="1500"/>
     <d v="2024-11-27T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1500"/>
@@ -14790,6 +15945,7 @@
     <n v="3200"/>
     <d v="2024-09-21T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1501"/>
@@ -14803,6 +15959,7 @@
     <n v="10000"/>
     <d v="2024-09-07T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1502"/>
@@ -14816,6 +15973,7 @@
     <n v="10000"/>
     <d v="2024-11-28T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1503"/>
@@ -14829,6 +15987,7 @@
     <n v="10000"/>
     <d v="2024-08-29T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1504"/>
@@ -14842,6 +16001,7 @@
     <n v="40000"/>
     <d v="2024-07-09T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1505"/>
@@ -14855,6 +16015,7 @@
     <n v="10000"/>
     <d v="2024-03-24T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1506"/>
@@ -14868,6 +16029,7 @@
     <n v="8000"/>
     <d v="2024-05-01T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1507"/>
@@ -14881,6 +16043,7 @@
     <n v="12500"/>
     <d v="2024-12-29T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1508"/>
@@ -14894,6 +16057,7 @@
     <n v="4500"/>
     <d v="2024-07-11T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1509"/>
@@ -14907,6 +16071,7 @@
     <n v="15000"/>
     <d v="2024-04-10T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1510"/>
@@ -14920,6 +16085,7 @@
     <n v="2400"/>
     <d v="2024-07-18T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1511"/>
@@ -14933,6 +16099,7 @@
     <n v="100000"/>
     <d v="2024-07-07T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1512"/>
@@ -14946,6 +16113,7 @@
     <n v="800"/>
     <d v="2024-04-23T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1513"/>
@@ -14959,6 +16127,7 @@
     <n v="15000"/>
     <d v="2024-02-29T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1514"/>
@@ -14972,6 +16141,7 @@
     <n v="3000"/>
     <d v="2024-05-16T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1515"/>
@@ -14985,6 +16155,7 @@
     <n v="2000"/>
     <d v="2024-08-23T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1516"/>
@@ -14998,6 +16169,7 @@
     <n v="1600"/>
     <d v="2024-10-28T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1517"/>
@@ -15011,6 +16183,7 @@
     <n v="15000"/>
     <d v="2024-01-01T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1518"/>
@@ -15024,6 +16197,7 @@
     <n v="100000"/>
     <d v="2024-01-04T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1519"/>
@@ -15037,6 +16211,7 @@
     <n v="100000"/>
     <d v="2024-10-20T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1520"/>
@@ -15050,6 +16225,7 @@
     <n v="1600"/>
     <d v="2024-12-02T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1521"/>
@@ -15063,6 +16239,7 @@
     <n v="800"/>
     <d v="2024-12-15T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1522"/>
@@ -15076,6 +16253,7 @@
     <n v="7500"/>
     <d v="2024-01-03T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1523"/>
@@ -15089,6 +16267,7 @@
     <n v="9000"/>
     <d v="2024-02-10T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1524"/>
@@ -15102,6 +16281,7 @@
     <n v="1500"/>
     <d v="2024-04-13T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1525"/>
@@ -15115,6 +16295,7 @@
     <n v="250000"/>
     <d v="2024-11-22T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1526"/>
@@ -15128,6 +16309,7 @@
     <n v="1600"/>
     <d v="2024-08-20T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1527"/>
@@ -15141,6 +16323,7 @@
     <n v="3200"/>
     <d v="2024-06-22T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1528"/>
@@ -15154,6 +16337,7 @@
     <n v="15000"/>
     <d v="2024-02-09T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1529"/>
@@ -15167,6 +16351,7 @@
     <n v="12500"/>
     <d v="2024-09-16T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1530"/>
@@ -15180,6 +16365,7 @@
     <n v="100000"/>
     <d v="2024-08-13T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1531"/>
@@ -15193,6 +16379,7 @@
     <n v="3200"/>
     <d v="2024-06-24T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1532"/>
@@ -15206,6 +16393,7 @@
     <n v="10000"/>
     <d v="2024-11-10T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1533"/>
@@ -15219,6 +16407,7 @@
     <n v="100000"/>
     <d v="2024-06-02T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1534"/>
@@ -15232,6 +16421,7 @@
     <n v="25000"/>
     <d v="2024-06-19T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1535"/>
@@ -15245,6 +16435,7 @@
     <n v="100000"/>
     <d v="2024-01-13T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1536"/>
@@ -15258,6 +16449,7 @@
     <n v="7500"/>
     <d v="2024-12-14T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1537"/>
@@ -15271,6 +16463,7 @@
     <n v="250000"/>
     <d v="2024-06-01T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1538"/>
@@ -15284,6 +16477,7 @@
     <n v="800"/>
     <d v="2024-12-19T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1539"/>
@@ -15297,6 +16491,7 @@
     <n v="3200"/>
     <d v="2024-11-16T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1540"/>
@@ -15310,6 +16505,7 @@
     <n v="3000"/>
     <d v="2024-05-10T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1541"/>
@@ -15323,6 +16519,7 @@
     <n v="10000"/>
     <d v="2024-07-21T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1542"/>
@@ -15336,6 +16533,7 @@
     <n v="2500"/>
     <d v="2024-12-23T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1543"/>
@@ -15349,6 +16547,7 @@
     <n v="4000"/>
     <d v="2024-02-28T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1544"/>
@@ -15362,6 +16561,7 @@
     <n v="40000"/>
     <d v="2024-03-02T00:00:00"/>
     <x v="0"/>
+    <m/>
   </r>
   <r>
     <n v="1545"/>
@@ -15375,6 +16575,7 @@
     <n v="2500"/>
     <d v="2024-11-06T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1546"/>
@@ -15388,6 +16589,7 @@
     <n v="20000"/>
     <d v="2024-07-10T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1547"/>
@@ -15401,6 +16603,7 @@
     <n v="12500"/>
     <d v="2024-07-27T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1548"/>
@@ -15414,6 +16617,7 @@
     <n v="40000"/>
     <d v="2024-02-08T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1549"/>
@@ -15427,6 +16631,7 @@
     <n v="15000"/>
     <d v="2024-09-16T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1550"/>
@@ -15440,6 +16645,7 @@
     <n v="9000"/>
     <d v="2024-02-08T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1551"/>
@@ -15453,6 +16659,7 @@
     <n v="40000"/>
     <d v="2024-10-21T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1552"/>
@@ -15466,6 +16673,7 @@
     <n v="4500"/>
     <d v="2024-08-08T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1553"/>
@@ -15479,6 +16687,7 @@
     <n v="3000"/>
     <d v="2024-10-31T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1554"/>
@@ -15492,6 +16701,7 @@
     <n v="15000"/>
     <d v="2024-08-07T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1555"/>
@@ -15505,6 +16715,7 @@
     <n v="12500"/>
     <d v="2024-02-12T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1556"/>
@@ -15518,6 +16729,7 @@
     <n v="3000"/>
     <d v="2024-08-07T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1557"/>
@@ -15531,6 +16743,7 @@
     <n v="4000"/>
     <d v="2024-08-09T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1558"/>
@@ -15544,6 +16757,7 @@
     <n v="8000"/>
     <d v="2024-07-30T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1559"/>
@@ -15557,6 +16771,7 @@
     <n v="6000"/>
     <d v="2024-09-03T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1560"/>
@@ -15570,6 +16785,7 @@
     <n v="1500"/>
     <d v="2024-05-09T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1561"/>
@@ -15583,6 +16799,7 @@
     <n v="2500"/>
     <d v="2024-09-20T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1562"/>
@@ -15596,6 +16813,7 @@
     <n v="2400"/>
     <d v="2024-11-08T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1563"/>
@@ -15609,6 +16827,7 @@
     <n v="10000"/>
     <d v="2024-04-14T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1564"/>
@@ -15622,6 +16841,7 @@
     <n v="3000"/>
     <d v="2024-07-30T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1565"/>
@@ -15635,6 +16855,7 @@
     <n v="5000"/>
     <d v="2024-01-25T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1566"/>
@@ -15648,6 +16869,7 @@
     <n v="2400"/>
     <d v="2024-01-14T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1567"/>
@@ -15661,6 +16883,7 @@
     <n v="7500"/>
     <d v="2024-10-21T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1568"/>
@@ -15674,6 +16897,7 @@
     <n v="800"/>
     <d v="2024-06-15T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1569"/>
@@ -15687,6 +16911,7 @@
     <n v="2400"/>
     <d v="2024-11-29T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1570"/>
@@ -15700,6 +16925,7 @@
     <n v="25000"/>
     <d v="2024-08-10T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1571"/>
@@ -15713,6 +16939,7 @@
     <n v="1500"/>
     <d v="2024-01-06T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1572"/>
@@ -15726,6 +16953,7 @@
     <n v="60000"/>
     <d v="2024-06-03T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1573"/>
@@ -15739,6 +16967,7 @@
     <n v="6000"/>
     <d v="2024-04-25T00:00:00"/>
     <x v="7"/>
+    <m/>
   </r>
   <r>
     <n v="1574"/>
@@ -15752,6 +16981,7 @@
     <n v="15000"/>
     <d v="2024-12-08T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1575"/>
@@ -15765,6 +16995,7 @@
     <n v="3000"/>
     <d v="2024-11-26T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1576"/>
@@ -15778,6 +17009,7 @@
     <n v="3000"/>
     <d v="2024-10-15T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1577"/>
@@ -15791,6 +17023,7 @@
     <n v="250000"/>
     <d v="2024-08-21T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1578"/>
@@ -15804,6 +17037,7 @@
     <n v="2500"/>
     <d v="2024-08-18T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1579"/>
@@ -15817,6 +17051,7 @@
     <n v="25000"/>
     <d v="2024-12-28T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1580"/>
@@ -15830,6 +17065,7 @@
     <n v="25000"/>
     <d v="2024-02-23T00:00:00"/>
     <x v="10"/>
+    <m/>
   </r>
   <r>
     <n v="1581"/>
@@ -15843,6 +17079,7 @@
     <n v="1500"/>
     <d v="2024-08-19T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1582"/>
@@ -15856,6 +17093,7 @@
     <n v="50000"/>
     <d v="2024-06-21T00:00:00"/>
     <x v="3"/>
+    <m/>
   </r>
   <r>
     <n v="1583"/>
@@ -15869,6 +17107,7 @@
     <n v="200000"/>
     <d v="2024-09-06T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1584"/>
@@ -15882,6 +17121,7 @@
     <n v="4000"/>
     <d v="2024-08-06T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1585"/>
@@ -15895,6 +17135,7 @@
     <n v="100000"/>
     <d v="2024-12-31T00:00:00"/>
     <x v="6"/>
+    <m/>
   </r>
   <r>
     <n v="1586"/>
@@ -15908,6 +17149,7 @@
     <n v="7500"/>
     <d v="2024-09-18T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1587"/>
@@ -15921,6 +17163,7 @@
     <n v="5000"/>
     <d v="2024-09-26T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1588"/>
@@ -15934,6 +17177,7 @@
     <n v="4000"/>
     <d v="2024-11-24T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1589"/>
@@ -15947,6 +17191,7 @@
     <n v="3000"/>
     <d v="2024-08-29T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1590"/>
@@ -15960,6 +17205,7 @@
     <n v="100000"/>
     <d v="2024-08-31T00:00:00"/>
     <x v="4"/>
+    <m/>
   </r>
   <r>
     <n v="1591"/>
@@ -15973,6 +17219,7 @@
     <n v="9000"/>
     <d v="2024-05-18T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1592"/>
@@ -15986,6 +17233,7 @@
     <n v="10000"/>
     <d v="2024-01-28T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1593"/>
@@ -15999,6 +17247,7 @@
     <n v="1500"/>
     <d v="2024-01-28T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1594"/>
@@ -16012,6 +17261,7 @@
     <n v="100000"/>
     <d v="2024-05-31T00:00:00"/>
     <x v="8"/>
+    <m/>
   </r>
   <r>
     <n v="1595"/>
@@ -16025,6 +17275,7 @@
     <n v="15000"/>
     <d v="2024-10-03T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
   <r>
     <n v="1596"/>
@@ -16038,6 +17289,7 @@
     <n v="50000"/>
     <d v="2024-01-30T00:00:00"/>
     <x v="11"/>
+    <m/>
   </r>
   <r>
     <n v="1597"/>
@@ -16051,6 +17303,7 @@
     <n v="9000"/>
     <d v="2024-07-25T00:00:00"/>
     <x v="5"/>
+    <m/>
   </r>
   <r>
     <n v="1598"/>
@@ -16064,6 +17317,7 @@
     <n v="100000"/>
     <d v="2024-11-13T00:00:00"/>
     <x v="9"/>
+    <m/>
   </r>
   <r>
     <n v="1599"/>
@@ -16077,6 +17331,7 @@
     <n v="5000"/>
     <d v="2024-09-08T00:00:00"/>
     <x v="2"/>
+    <m/>
   </r>
   <r>
     <n v="1600"/>
@@ -16090,19 +17345,20 @@
     <n v="9000"/>
     <d v="2024-10-09T00:00:00"/>
     <x v="1"/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="8">
+      <items count="9">
         <item x="5"/>
         <item x="3"/>
         <item x="1"/>
@@ -16110,15 +17366,17 @@
         <item x="0"/>
         <item x="6"/>
         <item x="2"/>
+        <item m="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
         <item x="2"/>
         <item x="1"/>
         <item x="0"/>
+        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16126,288 +17384,8 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="44">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="46">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7E09631-87F3-42CE-8B03-FB6B42A46D9B}" name="by cetegory" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="B3:C7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
@@ -16433,10 +17411,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="48">
+    <format dxfId="282">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="281">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16508,14 +17486,14 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="top cunsumer" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{347F2474-76D6-4630-9C84-DEDBE37C1E40}" name="top cunsumer" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B53:C66" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
+  <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="13">
+      <items count="14">
         <item x="8"/>
         <item x="10"/>
         <item x="3"/>
@@ -16528,11 +17506,12 @@
         <item x="11"/>
         <item x="6"/>
         <item x="5"/>
+        <item m="1" x="12"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="8">
+      <items count="9">
         <item x="5"/>
         <item x="3"/>
         <item x="1"/>
@@ -16540,15 +17519,17 @@
         <item x="0"/>
         <item x="6"/>
         <item x="2"/>
+        <item m="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="4">
+      <items count="5">
         <item x="2"/>
         <item x="1"/>
         <item x="0"/>
+        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16556,23 +17537,8 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="2"/>
@@ -16625,10 +17591,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="50">
+    <format dxfId="284">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="283">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16644,15 +17610,15 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF3BE05A-8DF4-4521-BB4B-B9788FA08E13}" name="by product" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="B23:C32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
+  <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="8">
+      <items count="9">
         <item x="5"/>
         <item x="3"/>
         <item x="1"/>
@@ -16660,11 +17626,12 @@
         <item x="0"/>
         <item x="6"/>
         <item x="2"/>
+        <item m="1" x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="9">
+      <items count="10">
         <item x="5"/>
         <item x="3"/>
         <item x="7"/>
@@ -16673,14 +17640,16 @@
         <item x="1"/>
         <item x="0"/>
         <item x="6"/>
+        <item m="1" x="8"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
-      <items count="4">
+      <items count="5">
         <item x="2"/>
         <item x="1"/>
         <item x="0"/>
+        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16688,23 +17657,8 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -16745,10 +17699,10 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="52">
+    <format dxfId="286">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="285">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -16880,6 +17834,262 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{109023CB-2C6A-4B0C-9CEB-FEC463F8C112}" name="monthly sales" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="B36:C49" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item m="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="11"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item m="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="288">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="287">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEB3E2F6-119A-4D03-96CE-D242796E1239}" name="by_city" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="B11:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item m="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item m="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="290">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="289">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{D33028C7-68A4-43A0-B516-720506AAE5EF}" sourceName="City">
   <pivotTables>
@@ -16890,7 +18100,7 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="601249990">
-      <items count="7">
+      <items count="8">
         <i x="5" s="1"/>
         <i x="3" s="1"/>
         <i x="1" s="1"/>
@@ -16898,6 +18108,7 @@
         <i x="0" s="1"/>
         <i x="6" s="1"/>
         <i x="2" s="1"/>
+        <i x="7" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -16914,10 +18125,11 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="601249990">
-      <items count="3">
+      <items count="4">
         <i x="2" s="1"/>
         <i x="1" s="1"/>
         <i x="0" s="1"/>
+        <i x="3" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -16932,11 +18144,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}" name="Ecommerce_Data" displayName="Ecommerce_Data" ref="A1:L602" totalsRowShown="0">
-  <autoFilter ref="A1:L602" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}" name="Ecommerce_Data" displayName="Ecommerce_Data" ref="A1:L601" totalsRowShown="0">
+  <autoFilter ref="A1:L601" xr:uid="{E9EB1D87-0387-424A-9FBA-25A5E111038F}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{308B8AE8-0EF3-4E00-90AB-55117EA19029}" name="Order ID"/>
-    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{59636E2C-7A39-472B-9321-57AA234D0B0B}" name="Order Date" dataDxfId="280"/>
     <tableColumn id="3" xr3:uid="{74135370-F89D-438A-B962-1CCD196557B1}" name="Customer Name"/>
     <tableColumn id="4" xr3:uid="{B474F51B-C2CB-4C85-A5EC-55BF075A01C9}" name="City"/>
     <tableColumn id="5" xr3:uid="{4939F22B-CA78-4718-98BD-CCB69768D3E0}" name="Product Name"/>
@@ -16944,8 +18156,8 @@
     <tableColumn id="7" xr3:uid="{6A004A32-99E0-4D3A-9463-C6C5B5320FE6}" name="Quantity"/>
     <tableColumn id="8" xr3:uid="{43C25B3C-200A-4AAC-B496-82A33D7E64F3}" name="Price"/>
     <tableColumn id="9" xr3:uid="{70B3244E-87E1-402D-A7F5-E4AC16E54570}" name="Total Sales"/>
-    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="41"/>
-    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="40">
+    <tableColumn id="12" xr3:uid="{F10E3F11-5915-4C79-84B2-53D40ED1EE14}" name="Order_Date" dataDxfId="279"/>
+    <tableColumn id="13" xr3:uid="{E59D46AD-691E-4CC6-BA8F-673D0988BF7F}" name="Month" dataDxfId="278">
       <calculatedColumnFormula>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{B0A5E0C2-382B-4A6A-89AF-DDA7D4F97E39}" name="Profit"/>
@@ -17238,476 +18450,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF3CD5B-B6B3-48EA-8FE8-F51E21FA5F4E}">
-  <dimension ref="B3:F66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="F3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1385000</v>
-      </c>
-      <c r="F4" s="6">
-        <f>SUM(Ecommerce_Data[Total Sales])</f>
-        <v>19158100</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5">
-        <v>16567500</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1205600</v>
-      </c>
-      <c r="F6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="5">
-        <v>19158100</v>
-      </c>
-      <c r="F7">
-        <f>COUNTA(Ecommerce_Data[Order ID])</f>
-        <v>601</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="F9" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2737200</v>
-      </c>
-      <c r="F12" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2996300</v>
-      </c>
-      <c r="F13">
-        <f>SUM(Ecommerce_Data[Total Sales]) / COUNTA(Ecommerce_Data[Order ID])</f>
-        <v>31877.038269550751</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1914000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="5">
-        <v>3072800</v>
-      </c>
-      <c r="F15" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2920500</v>
-      </c>
-      <c r="F16">
-        <f>SUM(Ecommerce_Data[Quantity])</f>
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="5">
-        <v>2604000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2913300</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C19" s="5">
-        <v>19158100</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="5">
-        <v>315000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5">
-        <v>587500</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="5">
-        <v>414000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="5">
-        <v>11400000</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="5">
-        <v>4580000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="5">
-        <v>606000</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="5">
-        <v>185600</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1070000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C32" s="5">
-        <v>19158100</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C37" s="5">
-        <v>2075900</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1004500</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C39" s="5">
-        <v>1088700</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C40" s="5">
-        <v>1215100</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C41" s="5">
-        <v>1553100</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="C42" s="5">
-        <v>2927200</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C43" s="5">
-        <v>1340000</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1671200</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1662900</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C46" s="5">
-        <v>1699400</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1319900</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C48" s="5">
-        <v>1600200</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C49" s="5">
-        <v>19158100</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" s="5">
-        <v>749900</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1526900</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B56" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1139000</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B57" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="5">
-        <v>2066300</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="5">
-        <v>1121800</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C59" s="5">
-        <v>2391600</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1752800</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B61" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="5">
-        <v>934900</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="5">
-        <v>1588100</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B63" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C63" s="5">
-        <v>3068200</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1144000</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B65" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C65" s="5">
-        <v>1674600</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B66" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C66" s="5">
-        <v>19158100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB32EC35-6A1C-458D-980E-B380654E859D}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
   <dimension ref="A3:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17730,9 +18476,493 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF3CD5B-B6B3-48EA-8FE8-F51E21FA5F4E}">
+  <dimension ref="B3:F67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1385000</v>
+      </c>
+      <c r="F4" s="6">
+        <f>SUM(Ecommerce_Data[Total Sales])</f>
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5">
+        <v>16567500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1205600</v>
+      </c>
+      <c r="F6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" s="5">
+        <v>19158100</v>
+      </c>
+      <c r="F7" t="str">
+        <f>"Total Oder " &amp; COUNTA(Ecommerce_Data[Order ID])</f>
+        <v>Total Oder 600</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2737200</v>
+      </c>
+      <c r="F12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2996300</v>
+      </c>
+      <c r="F13" s="7" t="str">
+        <f>"Oder Value " &amp; SUM(Ecommerce_Data[Total Sales]) / COUNTA(Ecommerce_Data[Order ID])</f>
+        <v>Oder Value 31930.1666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1914000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3072800</v>
+      </c>
+      <c r="F15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2920500</v>
+      </c>
+      <c r="F16">
+        <f>SUM(Ecommerce_Data[Quantity])</f>
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2604000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2913300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C19" s="5">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C20"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="5">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="5">
+        <v>587500</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="5">
+        <v>414000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="5">
+        <v>11400000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="5">
+        <v>4580000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="5">
+        <v>606000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="5">
+        <v>185600</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" s="5">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C33"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C37" s="5">
+        <v>2075900</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1004500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1088700</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1215100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1553100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C42" s="5">
+        <v>2927200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1340000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1671200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1662900</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1699400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1319900</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1600200</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C49" s="5">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C50"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="5">
+        <v>749900</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1526900</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1139000</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="5">
+        <v>2066300</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1121800</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" s="5">
+        <v>2391600</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1752800</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="5">
+        <v>934900</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1588100</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="5">
+        <v>3068200</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1144000</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="5">
+        <v>1674600</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C66" s="5">
+        <v>19158100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C67"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L602"/>
+  <dimension ref="A1:L601"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -39983,16 +41213,6 @@
         <v>Oct</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A602">
-        <v>1601</v>
-      </c>
-      <c r="J602" s="2"/>
-      <c r="K602" s="7" t="str">
-        <f>TEXT(Ecommerce_Data[[#This Row],[Order_Date]],"mmm")</f>
-        <v>Jan</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
